--- a/important_mails_2026-10-09.xlsx
+++ b/important_mails_2026-10-09.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H227"/>
+  <dimension ref="A1:H229"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -490,7 +490,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>last7</t>
+          <t>today</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -500,67 +500,21 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Thu, 8 Oct 2026 16:07:57 +0000</t>
+          <t>Fri, 9 Oct 2026 05:03:27 +0000</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Amazon Multichannel Fulfillment Team &lt;multichannelfulfillment@supplychain.amazon.com&gt;</t>
+          <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Please share your feedback on MCF</t>
+          <t>FBA reimbursement notification</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>Please share your feedback on MCF
-As a valued Multichannel Fulfillment (MCF) managed customer, we are interested in learning about your program feedback including new features that may benefit your business. This may help us understand how we can better meet your business needs and continue to improve the customer experience.
-(button)  Click here to complete survey  https://amazonexteu.qualtrics.com/jfe/form/SV_cOSOOyGQjgcTF54?Q_CHL=gl&amp;amp;Q_DL=EMD_7XHD09nVvjxfqAf_cOSOOyGQjgcTF54_CGC_i4S2zEfdL6jRC00&amp;amp;_g_=g
-This submission form is unique to your Seller account and can only be submitted once.
-DISCLAIMER: Please do not include any Personally Identifiable Information within this survey such as physical addresses, phone numbers, merchant tokens, email addresses, account data, etc.
-Thank you,
-Your Multichannel Fulfillment Team
-This survey is hosted by an external party Qualtrics.com, so the link above does not lead to our website. Your responses are subject to Amazon's Privacy Notice. If you have any concerns about the authenticity of this e-mail or to find out more about Amazon's survey program, please visit the Amazon Customer Service help page
-We hope you found this message to be u</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>店铺绩效类</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>Wed, 7 Oct 2026 05:17:16 +0000</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>FBA reimbursement notification</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr"/>
-      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -576,6 +530,65 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>产品链接/合规类</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>today</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 9 Oct 2026 07:35:36 +0000</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Submit missing VAT Registration Information</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr"/>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Amazon Services
+ 96
+ Submit missing VAT Registration Information
+ Hello,
+ We are reaching out as we have identified that the following VAT registration information is missing in your Seller Central account:
+ Country
+ Details
+ Czech Republic
+ Inventory
+ Spain
+ Inventory
+ Italy
+ Ship from Non-Place of Establishment
+ Amazon requires Selling Partners to submit valid VAT Registration Numbers, to ensure compliance with tax requirements.
+ What actions do I need to take?
+ To avoid any impact to your account, we encourage you to submit this information at your earliest convenience. In your “Tax Settings” page , in Seller Central:
+ 1. Add a valid VAT registration number for the countries listed above , with an address linked to those VRNs and with address nature assigned.
+ 2. Verify that all your Tax Information in Seller Central matches the information provided to the Tax Authorities .
+ Provide my VAT information
+ We recommend that you contact your tax advisor to understand your obligations in each country that you sell in.
+Make sure you always keep your Tax Information up-to-date in Seller Central, for all the countries in which you have an obligation.
+For more information, visit European </t>
+        </is>
+      </c>
+    </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
@@ -594,21 +607,67 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Tue, 6 Oct 2026 04:57:40 +0000</t>
+          <t>Thu, 8 Oct 2026 16:07:57 +0000</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
+          <t>Amazon Multichannel Fulfillment Team &lt;multichannelfulfillment@supplychain.amazon.com&gt;</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>FBA reimbursement notification</t>
+          <t>Please share your feedback on MCF</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr"/>
       <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Please share your feedback on MCF
+As a valued Multichannel Fulfillment (MCF) managed customer, we are interested in learning about your program feedback including new features that may benefit your business. This may help us understand how we can better meet your business needs and continue to improve the customer experience.
+(button)  Click here to complete survey  https://amazonexteu.qualtrics.com/jfe/form/SV_cOSOOyGQjgcTF54?Q_CHL=gl&amp;amp;Q_DL=EMD_7XHD09nVvjxfqAf_cOSOOyGQjgcTF54_CGC_i4S2zEfdL6jRC00&amp;amp;_g_=g
+This submission form is unique to your Seller account and can only be submitted once.
+DISCLAIMER: Please do not include any Personally Identifiable Information within this survey such as physical addresses, phone numbers, merchant tokens, email addresses, account data, etc.
+Thank you,
+Your Multichannel Fulfillment Team
+This survey is hosted by an external party Qualtrics.com, so the link above does not lead to our website. Your responses are subject to Amazon's Privacy Notice. If you have any concerns about the authenticity of this e-mail or to find out more about Amazon's survey program, please visit the Amazon Customer Service help page
+We hope you found this message to be u</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>店铺绩效类</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>last7</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 7 Oct 2026 05:17:16 +0000</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>FBA reimbursement notification</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -624,39 +683,87 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 6 Oct 2026 04:57:40 +0000</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>FBA reimbursement notification</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>96
+FBA reimbursement notification
+ You have a reimbursement activity
+ Hello from Fulfilment by Amazon,
+We have initiated a reimbursement, a reimbursement reversal, or both due to recent activity on your selling account. No action is required from you.
+Reimbursements can be initiated for an issue that you notified us about or one that we identified at a fulfilment centre. A reimbursement reversal occurs when a reimbursement decision has been reviewed and changed. Reimbursement amounts are determined in accordance with the FBA inventory reimbursement policy ( https://sellercentral.amazon.co.uk/gp/help/external/200213130 ).
+Please note that it may take up to five business days for reimbursement transactions to appear in your seller account.
+You can find details on your reimbursement or reversal transaction in the Reimbursements report ( https://sellercentral.amazon.co.uk/reportcentral/REIMBURSEMENTS/0 ) in Seller Central:
+- In the Event Date drop-down menu, select a date range and click Generate report . You can use the date in the subject line of this email as a point of reference.
+- To identify inventory reimbursements and reversals, see the Quantity reimbursed [inventory] column.
+-</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>店铺绩效类</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>last7</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>Sat, 3 Oct 2026 17:10:17 +0000</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr"/>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr"/>
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -677,39 +784,39 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>Sat, 3 Oct 2026 04:56:42 +0000</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr"/>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -722,106 +829,6 @@
 - In the Event Date drop-down menu, select a date range and click Generate report . You can use the date in the subject line of this email as a point of reference.
 - To identify inventory reimbursements and reversals, see the Quantity reimbursed [inventory] column.
 -</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>店铺绩效类</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 2 Oct 2026 04:48:02 +0000</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>FBA reimbursement notification</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr"/>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>96
-FBA reimbursement notification
- You have a reimbursement activity
- Hello from Fulfilment by Amazon,
-We have initiated a reimbursement, a reimbursement reversal, or both due to recent activity on your selling account. No action is required from you.
-Reimbursements can be initiated for an issue that you notified us about or one that we identified at a fulfilment centre. A reimbursement reversal occurs when a reimbursement decision has been reviewed and changed. Reimbursement amounts are determined in accordance with the FBA inventory reimbursement policy ( https://sellercentral.amazon.co.uk/gp/help/external/200213130 ).
-Please note that it may take up to five business days for reimbursement transactions to appear in your seller account.
-You can find details on your reimbursement or reversal transaction in the Reimbursements report ( https://sellercentral.amazon.co.uk/reportcentral/REIMBURSEMENTS/0 ) in Seller Central:
-- In the Event Date drop-down menu, select a date range and click Generate report . You can use the date in the subject line of this email as a point of reference.
-- To identify inventory reimbursements and reversals, see the Quantity reimbursed [inventory] column.
--</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>店铺绩效类</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 2 Oct 2026 03:23:37 +0000</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>Your FBA request is complete (Jl40SY3EId)</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr"/>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>Greetings from Amazon.com
-We thought you'd like to know that we have completed your destroy request.
-You can track the status of this request by visiting your Seller Account at:
-https://sellercentral-europe.amazon.com/
-For a complete list of inventory being destroyed, go to:
-https://sellercentral-europe.amazon.com/gp/orders/fba-order-details.html?orderID=S02-1559899-2958811
-Please note: this email was sent from a notification-only address that
-cannot accept incoming e-mail. Please do not reply to this message.
-Thank you for using Fulfillment by Amazon.
-------------------------------------------------------------------------------
-Fulfilment by Amazon – let Amazon pick, pack and ship your orders domestically
-and EU wide.
-------------------------------------------------------------------------------
-Was this e-mail helpful? https://sellercentral.amazon.co.uk/gp/satisfaction/survey-form.html?ie=UTF8&amp;HMDName=NotificationBusEmailHMD&amp;customAttribute1Value=PRODUCT_REMOVAL_ORDER_SHIPPED_NOW
-SPC-EUAmazon-387029790754281</t>
         </is>
       </c>
     </row>
@@ -5206,7 +5213,7 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>法务/侵权类</t>
+          <t>货件/库存类</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
@@ -5221,203 +5228,21 @@
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>Fri, 2 Oct 2026 08:41:07 +0000</t>
+          <t>Tue, 6 Oct 2026 20:20:03 +0000</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+          <t>Fulfilment by Amazon Operations &lt;fba-noreply@amazon.lu&gt;</t>
         </is>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>Zmiana kategorii opłat obowiązująca od 31 października 2026 r.</t>
+          <t>Your Amazon-Fulfilled Inventory</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr"/>
       <c r="H93" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">96
- Zmiana kategorii opłat w przypadku niektórych Twoich produktów w europejskich sklepach Amazon
- Dzień dobry,
-31 października 2026 r. niektóre Twoje produkty w europejskich sklepach Amazon zostaną przypisane do zaktualizowanych kategorii opłat.
-Kategorie opłat określają, jakim rodzajem produktu jest dany ASIN, przy czym mogą różnić się od kategorii, w których produkty są wystawione w naszych sklepach. Każdy produkt w naszym katalogu może należeć tylko do jednej kategorii opłat. Regularnie sprawdzamy produkty, aby mieć pewność, że zostały przypisane do odpowiednich kategorii opłat zgodnie z naszymi wytycznymi dotyczącymi kategorii opłat .
-To tylko aktualizacja kategorii opłat. Jednak po przypisaniu produktu do nowej kategorii opłaty mogą się zmienić, ponieważ różne kategorie mają różne struktury stawek.
-Aby sprawdzić swoje produkty, których dotyczy ta kwestia, i zaktualizowane stawki, pobierz raport o aktualizacji mojej kategorii opłat . Jeśli do danego ASIN masz przypisanych wiele kodów SKU, zmiany dotyczące kategorii opłat będą miały zastosowanie do wszystkich tych jednostek SKU.
-Aby dowiedzieć się więcej o stawkach opłat, przejdź na stronę Opłaty za sprzedaż na Amazon .
-Więcej </t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C94" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D94" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 2 Oct 2026 07:57:37 +0000</t>
-        </is>
-      </c>
-      <c r="E94" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F94" s="2" t="inlineStr">
-        <is>
-          <t>Actualización de las categorías de tarifas con entrada en vigor el 31 de octubre de 2026</t>
-        </is>
-      </c>
-      <c r="G94" s="2" t="inlineStr"/>
-      <c r="H94" s="2" t="inlineStr">
-        <is>
-          <t>96
- Se asignarán algunos de tus ASIN a otra categoría de tarifa en nuestras tiendas europeas.
- Hola:
-Con entrada en vigor el 31 de octubre de 2026, se asignarán algunos de tus ASIN en nuestras tiendas europeas a categorías de tarifas actualizadas.
-Las categorías de tarifas describen qué tipo de producto es un ASIN y pueden ser diferentes de la categoría en la que aparece el ASIN en nuestras tiendas. Cada ASIN de nuestro catálogo sólo puede pertenecer a una única categoría de tarifas. De forma periódica, revisamos los ASIN para asegurarnos de que tengan asignadas las categorías de tarifas correctas, tal y como se muestra en nuestras directrices de las categorías de tarifas .
-Sólo hemos actualizado las categorías de tarifas. Sin embargo, tus tarifas pueden variar cuando se asigne tu ASIN a una categoría nueva, ya que cada categoría tiene una estructura de tarifas distinta.
-Para consultar los ASIN afectados y sus tarifas actualizadas, descarga el Informe de actualización de categorías de tarifas . Si tienes varios SKU para el mismo ASIN, los cambios de categoría se aplicarán a todos los SKU.
-Para más información sobre las tarifas, consulta Tabla de tarifas de Vender en Amazon .
-Para m</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C95" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D95" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 2 Oct 2026 07:49:32 +0000</t>
-        </is>
-      </c>
-      <c r="E95" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F95" s="2" t="inlineStr">
-        <is>
-          <t>Categorie di commissioni aggiornate dal 31 ottobre 2026</t>
-        </is>
-      </c>
-      <c r="G95" s="2" t="inlineStr"/>
-      <c r="H95" s="2" t="inlineStr">
-        <is>
-          <t>96
- Alcuni dei tuoi ASIN verranno assegnati a una categoria di commissioni diversa nei nostri negozi europei
- Buongiorno,
-A partire dal 31 ottobre 2026, alcuni dei tuoi ASIN nei nostri negozi europei verranno assegnati a categorie di commissioni aggiornate.
-Le categorie di commissioni descrivono la tipologia di prodotto degli ASIN e possono essere diverse dalle categorie sotto alle quali gli stessi ASIN compaiono nei negozi Amazon. Ogni ASIN presente nel nostro catalogo può appartenere a una sola categoria di commissioni. Verifichiamo regolarmente gli ASIN per garantire che siano assegnati alle categorie di commissioni corrette, come indicato nelle nostre linee guida sulle categorie di commissioni .
-Questo aggiornamento riguarda esclusivamente le categorie di commissioni. Tuttavia, le tue commissioni potrebbero variare quando l'ASIN viene assegnato a una nuova categoria, perché categorie diverse prevedono strutture tariffarie diverse.
-Per consultare gli ASIN interessati e i relativi costi aggiornati, scarica il tuo report sulle modifiche alle categorie di tariffe e commissioni . Se disponi di più SKU per lo stesso ASIN, queste modifiche saranno applicate a tutti gli SKU.
-Per maggio</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C96" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D96" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 2 Oct 2026 07:46:36 +0000</t>
-        </is>
-      </c>
-      <c r="E96" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F96" s="2" t="inlineStr">
-        <is>
-          <t>Update van kostencategorieën, met ingang van 31 oktober 2026</t>
-        </is>
-      </c>
-      <c r="G96" s="2" t="inlineStr"/>
-      <c r="H96" s="2" t="inlineStr">
-        <is>
-          <t>96
- Enkele van je ASIN-codes worden toegewezen aan een andere kostencategorie in onze Europese winkels
- Hallo,
-Met ingang van 31 oktober 2026 worden enkele van jouw ASIN-codes in onze Europese winkels toegewezen aan bijgewerkte kostencategorieën.
-Kostencategorieën beschrijven wat voor soort product een ASIN is en kunnen verschillen van de categorie waarin het ASIN in onze winkels wordt weergegeven. Elk ASIN in onze catalogus kan tot slechts één kostencategorie behoren. We controleren regelmatig ASIN-codes om er zeker van te zijn dat ze aan de juiste kostencategorieën toegewezen zijn, zoals weergegeven in onze Richtlijnen voor kostencategorieën .
-Dit is alleen een update van de kostencategorie. Je kosten kunnen echter verschillen als je ASIN wordt toegewezen aan een nieuwe categorie omdat verschillende categorieën verschillende tariefstructuren hebben.
-Download Mijn overzicht van wijzigingen van kostencategorie om je betreffende ASIN-codes en hun bijgewerkte tarieven te bekijken. Als je meerdere SKU-codes hebt voor hetzelfde ASIN, zijn categoriewijzigingen van toepassing op alle SKU-codes.
-Ga naar het Kostenoverzicht voor Verkopen via Amazon voor meer informatie over kostentarieven.</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="2" t="inlineStr">
-        <is>
-          <t>货件/库存类</t>
-        </is>
-      </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C97" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D97" s="2" t="inlineStr">
-        <is>
-          <t>Tue, 6 Oct 2026 20:20:03 +0000</t>
-        </is>
-      </c>
-      <c r="E97" s="2" t="inlineStr">
-        <is>
-          <t>Fulfilment by Amazon Operations &lt;fba-noreply@amazon.lu&gt;</t>
-        </is>
-      </c>
-      <c r="F97" s="2" t="inlineStr">
-        <is>
-          <t>Your Amazon-Fulfilled Inventory</t>
-        </is>
-      </c>
-      <c r="G97" s="2" t="inlineStr"/>
-      <c r="H97" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 We recently notified you about the removal of your listing(s) for the product(s) listed below due to a safety recall.
@@ -5433,39 +5258,39 @@
         </is>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" s="2" t="inlineStr">
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B98" s="2" t="inlineStr">
+      <c r="B94" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C98" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D98" s="2" t="inlineStr">
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
         <is>
           <t>Sun, 4 Oct 2026 20:33:01 +0000</t>
         </is>
       </c>
-      <c r="E98" s="2" t="inlineStr">
+      <c r="E94" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon Operations &lt;fba-noreply@amazon.lu&gt;</t>
         </is>
       </c>
-      <c r="F98" s="2" t="inlineStr">
+      <c r="F94" s="2" t="inlineStr">
         <is>
           <t>Your Amazon-Fulfilled Inventory</t>
         </is>
       </c>
-      <c r="G98" s="2" t="inlineStr"/>
-      <c r="H98" s="2" t="inlineStr">
+      <c r="G94" s="2" t="inlineStr"/>
+      <c r="H94" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 We recently notified you about the removal of your listing(s) for the product(s) listed below due to a safety recall.
@@ -5481,39 +5306,39 @@
         </is>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" s="2" t="inlineStr">
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B99" s="2" t="inlineStr">
+      <c r="B95" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C99" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D99" s="2" t="inlineStr">
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
         <is>
           <t>Sat, 3 Oct 2026 03:07:33 +0000</t>
         </is>
       </c>
-      <c r="E99" s="2" t="inlineStr">
+      <c r="E95" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F99" s="2" t="inlineStr">
+      <c r="F95" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-10-15</t>
         </is>
       </c>
-      <c r="G99" s="2" t="inlineStr"/>
-      <c r="H99" s="2" t="inlineStr">
+      <c r="G95" s="2" t="inlineStr"/>
+      <c r="H95" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -5537,39 +5362,139 @@
         </is>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" s="2" t="inlineStr">
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C100" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D100" s="2" t="inlineStr">
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 2 Oct 2026 04:48:02 +0000</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>FBA reimbursement notification</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr"/>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>96
+FBA reimbursement notification
+ You have a reimbursement activity
+ Hello from Fulfilment by Amazon,
+We have initiated a reimbursement, a reimbursement reversal, or both due to recent activity on your selling account. No action is required from you.
+Reimbursements can be initiated for an issue that you notified us about or one that we identified at a fulfilment centre. A reimbursement reversal occurs when a reimbursement decision has been reviewed and changed. Reimbursement amounts are determined in accordance with the FBA inventory reimbursement policy ( https://sellercentral.amazon.co.uk/gp/help/external/200213130 ).
+Please note that it may take up to five business days for reimbursement transactions to appear in your seller account.
+You can find details on your reimbursement or reversal transaction in the Reimbursements report ( https://sellercentral.amazon.co.uk/reportcentral/REIMBURSEMENTS/0 ) in Seller Central:
+- In the Event Date drop-down menu, select a date range and click Generate report . You can use the date in the subject line of this email as a point of reference.
+- To identify inventory reimbursements and reversals, see the Quantity reimbursed [inventory] column.
+-</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>店铺绩效类</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 2 Oct 2026 03:23:37 +0000</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>Your FBA request is complete (Jl40SY3EId)</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr"/>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>Greetings from Amazon.com
+We thought you'd like to know that we have completed your destroy request.
+You can track the status of this request by visiting your Seller Account at:
+https://sellercentral-europe.amazon.com/
+For a complete list of inventory being destroyed, go to:
+https://sellercentral-europe.amazon.com/gp/orders/fba-order-details.html?orderID=S02-1559899-2958811
+Please note: this email was sent from a notification-only address that
+cannot accept incoming e-mail. Please do not reply to this message.
+Thank you for using Fulfillment by Amazon.
+------------------------------------------------------------------------------
+Fulfilment by Amazon – let Amazon pick, pack and ship your orders domestically
+and EU wide.
+------------------------------------------------------------------------------
+Was this e-mail helpful? https://sellercentral.amazon.co.uk/gp/satisfaction/survey-form.html?ie=UTF8&amp;HMDName=NotificationBusEmailHMD&amp;customAttribute1Value=PRODUCT_REMOVAL_ORDER_SHIPPED_NOW
+SPC-EUAmazon-387029790754281</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>店铺绩效类</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
         <is>
           <t>Tue, 29 Sep 2026 19:30:09 +0000</t>
         </is>
       </c>
-      <c r="E100" s="2" t="inlineStr">
+      <c r="E98" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F100" s="2" t="inlineStr">
+      <c r="F98" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (4sQeBGpWIe)</t>
         </is>
       </c>
-      <c r="G100" s="2" t="inlineStr"/>
-      <c r="H100" s="2" t="inlineStr">
+      <c r="G98" s="2" t="inlineStr"/>
+      <c r="H98" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -5589,39 +5514,39 @@
         </is>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" s="2" t="inlineStr">
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C101" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D101" s="2" t="inlineStr">
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
         <is>
           <t>Tue, 29 Sep 2026 09:21:47 +0000</t>
         </is>
       </c>
-      <c r="E101" s="2" t="inlineStr">
+      <c r="E99" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F101" s="2" t="inlineStr">
+      <c r="F99" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G101" s="2" t="inlineStr"/>
-      <c r="H101" s="2" t="inlineStr">
+      <c r="G99" s="2" t="inlineStr"/>
+      <c r="H99" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -5637,39 +5562,39 @@
         </is>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" s="2" t="inlineStr">
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C102" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D102" s="2" t="inlineStr">
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
         <is>
           <t>Tue, 29 Sep 2026 05:14:04 +0000</t>
         </is>
       </c>
-      <c r="E102" s="2" t="inlineStr">
+      <c r="E100" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F102" s="2" t="inlineStr">
+      <c r="F100" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G102" s="2" t="inlineStr"/>
-      <c r="H102" s="2" t="inlineStr">
+      <c r="G100" s="2" t="inlineStr"/>
+      <c r="H100" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -5685,39 +5610,39 @@
         </is>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" s="2" t="inlineStr">
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C103" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D103" s="2" t="inlineStr">
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
         <is>
           <t>Mon, 28 Sep 2026 05:02:53 +0000</t>
         </is>
       </c>
-      <c r="E103" s="2" t="inlineStr">
+      <c r="E101" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F103" s="2" t="inlineStr">
+      <c r="F101" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G103" s="2" t="inlineStr"/>
-      <c r="H103" s="2" t="inlineStr">
+      <c r="G101" s="2" t="inlineStr"/>
+      <c r="H101" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -5733,39 +5658,39 @@
         </is>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" s="2" t="inlineStr">
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C104" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D104" s="2" t="inlineStr">
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
         <is>
           <t>Sun, 27 Sep 2026 23:20:30 +0000</t>
         </is>
       </c>
-      <c r="E104" s="2" t="inlineStr">
+      <c r="E102" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F104" s="2" t="inlineStr">
+      <c r="F102" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (cENUYoUvou)</t>
         </is>
       </c>
-      <c r="G104" s="2" t="inlineStr"/>
-      <c r="H104" s="2" t="inlineStr">
+      <c r="G102" s="2" t="inlineStr"/>
+      <c r="H102" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -5790,39 +5715,39 @@
         </is>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" s="2" t="inlineStr">
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C105" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D105" s="2" t="inlineStr">
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
         <is>
           <t>Sun, 27 Sep 2026 04:48:00 +0000</t>
         </is>
       </c>
-      <c r="E105" s="2" t="inlineStr">
+      <c r="E103" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F105" s="2" t="inlineStr">
+      <c r="F103" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G105" s="2" t="inlineStr"/>
-      <c r="H105" s="2" t="inlineStr">
+      <c r="G103" s="2" t="inlineStr"/>
+      <c r="H103" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -5838,39 +5763,39 @@
         </is>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" s="2" t="inlineStr">
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C106" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D106" s="2" t="inlineStr">
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
         <is>
           <t>Sat, 26 Sep 2026 16:39:11 +0000</t>
         </is>
       </c>
-      <c r="E106" s="2" t="inlineStr">
+      <c r="E104" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F106" s="2" t="inlineStr">
+      <c r="F104" s="2" t="inlineStr">
         <is>
           <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
-      <c r="G106" s="2" t="inlineStr"/>
-      <c r="H106" s="2" t="inlineStr">
+      <c r="G104" s="2" t="inlineStr"/>
+      <c r="H104" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -5891,39 +5816,39 @@
         </is>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" s="2" t="inlineStr">
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C107" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D107" s="2" t="inlineStr">
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
         <is>
           <t>Fri, 25 Sep 2026 04:50:51 +0000</t>
         </is>
       </c>
-      <c r="E107" s="2" t="inlineStr">
+      <c r="E105" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F107" s="2" t="inlineStr">
+      <c r="F105" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G107" s="2" t="inlineStr"/>
-      <c r="H107" s="2" t="inlineStr">
+      <c r="G105" s="2" t="inlineStr"/>
+      <c r="H105" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -5939,39 +5864,39 @@
         </is>
       </c>
     </row>
-    <row r="108">
-      <c r="A108" s="2" t="inlineStr">
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C108" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D108" s="2" t="inlineStr">
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
         <is>
           <t>Thu, 24 Sep 2026 04:54:38 +0000</t>
         </is>
       </c>
-      <c r="E108" s="2" t="inlineStr">
+      <c r="E106" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F108" s="2" t="inlineStr">
+      <c r="F106" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G108" s="2" t="inlineStr"/>
-      <c r="H108" s="2" t="inlineStr">
+      <c r="G106" s="2" t="inlineStr"/>
+      <c r="H106" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -5987,39 +5912,39 @@
         </is>
       </c>
     </row>
-    <row r="109">
-      <c r="A109" s="2" t="inlineStr">
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C109" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D109" s="2" t="inlineStr">
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
         <is>
           <t>Wed, 23 Sep 2026 16:43:27 +0000</t>
         </is>
       </c>
-      <c r="E109" s="2" t="inlineStr">
+      <c r="E107" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F109" s="2" t="inlineStr">
+      <c r="F107" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (7iKN0D3u4y)</t>
         </is>
       </c>
-      <c r="G109" s="2" t="inlineStr"/>
-      <c r="H109" s="2" t="inlineStr">
+      <c r="G107" s="2" t="inlineStr"/>
+      <c r="H107" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -6039,39 +5964,39 @@
         </is>
       </c>
     </row>
-    <row r="110">
-      <c r="A110" s="2" t="inlineStr">
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C110" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D110" s="2" t="inlineStr">
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
         <is>
           <t>Wed, 23 Sep 2026 09:25:48 +0000</t>
         </is>
       </c>
-      <c r="E110" s="2" t="inlineStr">
+      <c r="E108" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F110" s="2" t="inlineStr">
+      <c r="F108" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G110" s="2" t="inlineStr"/>
-      <c r="H110" s="2" t="inlineStr">
+      <c r="G108" s="2" t="inlineStr"/>
+      <c r="H108" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -6087,39 +6012,39 @@
         </is>
       </c>
     </row>
-    <row r="111">
-      <c r="A111" s="2" t="inlineStr">
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C111" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D111" s="2" t="inlineStr">
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
         <is>
           <t>Wed, 23 Sep 2026 05:04:18 +0000</t>
         </is>
       </c>
-      <c r="E111" s="2" t="inlineStr">
+      <c r="E109" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F111" s="2" t="inlineStr">
+      <c r="F109" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G111" s="2" t="inlineStr"/>
-      <c r="H111" s="2" t="inlineStr">
+      <c r="G109" s="2" t="inlineStr"/>
+      <c r="H109" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -6135,39 +6060,39 @@
         </is>
       </c>
     </row>
-    <row r="112">
-      <c r="A112" s="2" t="inlineStr">
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C112" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D112" s="2" t="inlineStr">
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
         <is>
           <t>Tue, 22 Sep 2026 14:06:30 +0000</t>
         </is>
       </c>
-      <c r="E112" s="2" t="inlineStr">
+      <c r="E110" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F112" s="2" t="inlineStr">
+      <c r="F110" s="2" t="inlineStr">
         <is>
           <t>Address variation policy violations</t>
         </is>
       </c>
-      <c r="G112" s="2" t="inlineStr"/>
-      <c r="H112" s="2" t="inlineStr">
+      <c r="G110" s="2" t="inlineStr"/>
+      <c r="H110" s="2" t="inlineStr">
         <is>
           <t>96
  Address variation policy violations
@@ -6183,39 +6108,39 @@
         </is>
       </c>
     </row>
-    <row r="113">
-      <c r="A113" s="2" t="inlineStr">
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C113" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D113" s="2" t="inlineStr">
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
         <is>
           <t>Tue, 22 Sep 2026 04:54:44 +0000</t>
         </is>
       </c>
-      <c r="E113" s="2" t="inlineStr">
+      <c r="E111" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F113" s="2" t="inlineStr">
+      <c r="F111" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G113" s="2" t="inlineStr"/>
-      <c r="H113" s="2" t="inlineStr">
+      <c r="G111" s="2" t="inlineStr"/>
+      <c r="H111" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -6231,39 +6156,39 @@
         </is>
       </c>
     </row>
-    <row r="114">
-      <c r="A114" s="2" t="inlineStr">
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C114" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D114" s="2" t="inlineStr">
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
         <is>
           <t>Sun, 20 Sep 2026 14:23:10 +0000</t>
         </is>
       </c>
-      <c r="E114" s="2" t="inlineStr">
+      <c r="E112" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F114" s="2" t="inlineStr">
+      <c r="F112" s="2" t="inlineStr">
         <is>
           <t>Balance paid on your Amazon seller account</t>
         </is>
       </c>
-      <c r="G114" s="2" t="inlineStr"/>
-      <c r="H114" s="2" t="inlineStr">
+      <c r="G112" s="2" t="inlineStr"/>
+      <c r="H112" s="2" t="inlineStr">
         <is>
           <t>96
 Balance paid on your Amazon seller account
@@ -6286,39 +6211,39 @@
         </is>
       </c>
     </row>
-    <row r="115">
-      <c r="A115" s="2" t="inlineStr">
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C115" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D115" s="2" t="inlineStr">
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
         <is>
           <t>Sat, 19 Sep 2026 04:50:14 +0000</t>
         </is>
       </c>
-      <c r="E115" s="2" t="inlineStr">
+      <c r="E113" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F115" s="2" t="inlineStr">
+      <c r="F113" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G115" s="2" t="inlineStr"/>
-      <c r="H115" s="2" t="inlineStr">
+      <c r="G113" s="2" t="inlineStr"/>
+      <c r="H113" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -6334,39 +6259,39 @@
         </is>
       </c>
     </row>
-    <row r="116">
-      <c r="A116" s="2" t="inlineStr">
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C116" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D116" s="2" t="inlineStr">
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
         <is>
           <t>Fri, 18 Sep 2026 05:13:12 +0000</t>
         </is>
       </c>
-      <c r="E116" s="2" t="inlineStr">
+      <c r="E114" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F116" s="2" t="inlineStr">
+      <c r="F114" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G116" s="2" t="inlineStr"/>
-      <c r="H116" s="2" t="inlineStr">
+      <c r="G114" s="2" t="inlineStr"/>
+      <c r="H114" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -6382,39 +6307,39 @@
         </is>
       </c>
     </row>
-    <row r="117">
-      <c r="A117" s="2" t="inlineStr">
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B117" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C117" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D117" s="2" t="inlineStr">
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
         <is>
           <t>Thu, 17 Sep 2026 04:57:09 +0000</t>
         </is>
       </c>
-      <c r="E117" s="2" t="inlineStr">
+      <c r="E115" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F117" s="2" t="inlineStr">
+      <c r="F115" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G117" s="2" t="inlineStr"/>
-      <c r="H117" s="2" t="inlineStr">
+      <c r="G115" s="2" t="inlineStr"/>
+      <c r="H115" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -6430,39 +6355,39 @@
         </is>
       </c>
     </row>
-    <row r="118">
-      <c r="A118" s="2" t="inlineStr">
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C118" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D118" s="2" t="inlineStr">
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
         <is>
           <t>Wed, 16 Sep 2026 07:03:28 +0000</t>
         </is>
       </c>
-      <c r="E118" s="2" t="inlineStr">
+      <c r="E116" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F118" s="2" t="inlineStr">
+      <c r="F116" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G118" s="2" t="inlineStr"/>
-      <c r="H118" s="2" t="inlineStr">
+      <c r="G116" s="2" t="inlineStr"/>
+      <c r="H116" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -6478,39 +6403,39 @@
         </is>
       </c>
     </row>
-    <row r="119">
-      <c r="A119" s="2" t="inlineStr">
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B119" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C119" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D119" s="2" t="inlineStr">
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
         <is>
           <t>Tue, 15 Sep 2026 09:36:39 +0000</t>
         </is>
       </c>
-      <c r="E119" s="2" t="inlineStr">
+      <c r="E117" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F119" s="2" t="inlineStr">
+      <c r="F117" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G119" s="2" t="inlineStr"/>
-      <c r="H119" s="2" t="inlineStr">
+      <c r="G117" s="2" t="inlineStr"/>
+      <c r="H117" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -6526,39 +6451,39 @@
         </is>
       </c>
     </row>
-    <row r="120">
-      <c r="A120" s="2" t="inlineStr">
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C120" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D120" s="2" t="inlineStr">
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
         <is>
           <t>Sun, 13 Sep 2026 04:42:34 +0000</t>
         </is>
       </c>
-      <c r="E120" s="2" t="inlineStr">
+      <c r="E118" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F120" s="2" t="inlineStr">
+      <c r="F118" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G120" s="2" t="inlineStr"/>
-      <c r="H120" s="2" t="inlineStr">
+      <c r="G118" s="2" t="inlineStr"/>
+      <c r="H118" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -6574,39 +6499,39 @@
         </is>
       </c>
     </row>
-    <row r="121">
-      <c r="A121" s="2" t="inlineStr">
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B121" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C121" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D121" s="2" t="inlineStr">
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
         <is>
           <t>Sat, 12 Sep 2026 04:52:40 +0000</t>
         </is>
       </c>
-      <c r="E121" s="2" t="inlineStr">
+      <c r="E119" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F121" s="2" t="inlineStr">
+      <c r="F119" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G121" s="2" t="inlineStr"/>
-      <c r="H121" s="2" t="inlineStr">
+      <c r="G119" s="2" t="inlineStr"/>
+      <c r="H119" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -6622,39 +6547,39 @@
         </is>
       </c>
     </row>
-    <row r="122">
-      <c r="A122" s="2" t="inlineStr">
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C122" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D122" s="2" t="inlineStr">
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
         <is>
           <t>Fri, 11 Sep 2026 09:37:22 +0000</t>
         </is>
       </c>
-      <c r="E122" s="2" t="inlineStr">
+      <c r="E120" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F122" s="2" t="inlineStr">
+      <c r="F120" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G122" s="2" t="inlineStr"/>
-      <c r="H122" s="2" t="inlineStr">
+      <c r="G120" s="2" t="inlineStr"/>
+      <c r="H120" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -6670,39 +6595,39 @@
         </is>
       </c>
     </row>
-    <row r="123">
-      <c r="A123" s="2" t="inlineStr">
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B123" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C123" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D123" s="2" t="inlineStr">
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
         <is>
           <t>Fri, 11 Sep 2026 05:39:06 +0000</t>
         </is>
       </c>
-      <c r="E123" s="2" t="inlineStr">
+      <c r="E121" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F123" s="2" t="inlineStr">
+      <c r="F121" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G123" s="2" t="inlineStr"/>
-      <c r="H123" s="2" t="inlineStr">
+      <c r="G121" s="2" t="inlineStr"/>
+      <c r="H121" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -6718,39 +6643,39 @@
         </is>
       </c>
     </row>
-    <row r="124">
-      <c r="A124" s="2" t="inlineStr">
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C124" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D124" s="2" t="inlineStr">
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
         <is>
           <t>Thu, 10 Sep 2026 09:08:38 +0000</t>
         </is>
       </c>
-      <c r="E124" s="2" t="inlineStr">
+      <c r="E122" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F124" s="2" t="inlineStr">
+      <c r="F122" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G124" s="2" t="inlineStr"/>
-      <c r="H124" s="2" t="inlineStr">
+      <c r="G122" s="2" t="inlineStr"/>
+      <c r="H122" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -6766,39 +6691,39 @@
         </is>
       </c>
     </row>
-    <row r="125">
-      <c r="A125" s="2" t="inlineStr">
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B125" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C125" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D125" s="2" t="inlineStr">
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
         <is>
           <t>Thu, 10 Sep 2026 05:04:40 +0000</t>
         </is>
       </c>
-      <c r="E125" s="2" t="inlineStr">
+      <c r="E123" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F125" s="2" t="inlineStr">
+      <c r="F123" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G125" s="2" t="inlineStr"/>
-      <c r="H125" s="2" t="inlineStr">
+      <c r="G123" s="2" t="inlineStr"/>
+      <c r="H123" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -6814,39 +6739,39 @@
         </is>
       </c>
     </row>
-    <row r="126">
-      <c r="A126" s="2" t="inlineStr">
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C126" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D126" s="2" t="inlineStr">
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
         <is>
           <t>Wed, 9 Sep 2026 11:29:22 +0000</t>
         </is>
       </c>
-      <c r="E126" s="2" t="inlineStr">
+      <c r="E124" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F126" s="2" t="inlineStr">
+      <c r="F124" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (YHD3zckrc9)</t>
         </is>
       </c>
-      <c r="G126" s="2" t="inlineStr"/>
-      <c r="H126" s="2" t="inlineStr">
+      <c r="G124" s="2" t="inlineStr"/>
+      <c r="H124" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -6866,39 +6791,39 @@
         </is>
       </c>
     </row>
-    <row r="127">
-      <c r="A127" s="2" t="inlineStr">
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
         <is>
           <t>KYC审核类</t>
         </is>
       </c>
-      <c r="B127" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C127" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D127" s="2" t="inlineStr">
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
         <is>
           <t>Sun, 20 Sep 2026 05:13:35 +0000</t>
         </is>
       </c>
-      <c r="E127" s="2" t="inlineStr">
+      <c r="E125" s="2" t="inlineStr">
         <is>
           <t>"Amazon.it" &lt;store-news@amazon.it&gt;</t>
         </is>
       </c>
-      <c r="F127" s="2" t="inlineStr">
+      <c r="F125" s="2" t="inlineStr">
         <is>
           <t>Il tuo carrello chiama</t>
         </is>
       </c>
-      <c r="G127" s="2" t="inlineStr"/>
-      <c r="H127" s="2" t="inlineStr">
+      <c r="G125" s="2" t="inlineStr"/>
+      <c r="H125" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.it/gp/cart/view.html?ref_=cor
 Pista ferroviaria elettrica a cubi da 145 pezzi, set trenino 3D antigravità, gioco fai da te per costruire percorsi, giocattolo educativo STEM e idea regalo creativa per bambini da 3 a 8 anni
@@ -6919,39 +6844,39 @@
         </is>
       </c>
     </row>
-    <row r="128">
-      <c r="A128" s="2" t="inlineStr">
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C128" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D128" s="2" t="inlineStr">
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
         <is>
           <t>Thu, 1 Oct 2026 14:51:16 +0000</t>
         </is>
       </c>
-      <c r="E128" s="2" t="inlineStr">
+      <c r="E126" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F128" s="2" t="inlineStr">
+      <c r="F126" s="2" t="inlineStr">
         <is>
           <t>Twoja płatność jest już w drodze</t>
         </is>
       </c>
-      <c r="G128" s="2" t="inlineStr"/>
-      <c r="H128" s="2" t="inlineStr">
+      <c r="G126" s="2" t="inlineStr"/>
+      <c r="H126" s="2" t="inlineStr">
         <is>
           <t>96
 Ten tytuł będzie wyświetlany na urządzeniach mobilnych
@@ -6967,39 +6892,39 @@
         </is>
       </c>
     </row>
-    <row r="129">
-      <c r="A129" s="2" t="inlineStr">
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B129" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C129" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D129" s="2" t="inlineStr">
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
         <is>
           <t>Sat, 26 Sep 2026 13:36:40 +0000</t>
         </is>
       </c>
-      <c r="E129" s="2" t="inlineStr">
+      <c r="E127" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F129" s="2" t="inlineStr">
+      <c r="F127" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G129" s="2" t="inlineStr"/>
-      <c r="H129" s="2" t="inlineStr">
+      <c r="G127" s="2" t="inlineStr"/>
+      <c r="H127" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -7019,39 +6944,39 @@
         </is>
       </c>
     </row>
-    <row r="130">
-      <c r="A130" s="2" t="inlineStr">
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C130" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D130" s="2" t="inlineStr">
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
         <is>
           <t>Sat, 26 Sep 2026 13:33:11 +0000</t>
         </is>
       </c>
-      <c r="E130" s="2" t="inlineStr">
+      <c r="E128" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F130" s="2" t="inlineStr">
+      <c r="F128" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G130" s="2" t="inlineStr"/>
-      <c r="H130" s="2" t="inlineStr">
+      <c r="G128" s="2" t="inlineStr"/>
+      <c r="H128" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 This title will display on mobile devices
@@ -7071,39 +6996,39 @@
         </is>
       </c>
     </row>
-    <row r="131">
-      <c r="A131" s="2" t="inlineStr">
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B131" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C131" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D131" s="2" t="inlineStr">
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
         <is>
           <t>Sat, 26 Sep 2026 00:41:51 +0000</t>
         </is>
       </c>
-      <c r="E131" s="2" t="inlineStr">
+      <c r="E129" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F131" s="2" t="inlineStr">
+      <c r="F129" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G131" s="2" t="inlineStr"/>
-      <c r="H131" s="2" t="inlineStr">
+      <c r="G129" s="2" t="inlineStr"/>
+      <c r="H129" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 This title will display on mobile devices
@@ -7123,39 +7048,39 @@
         </is>
       </c>
     </row>
-    <row r="132">
-      <c r="A132" s="2" t="inlineStr">
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B132" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C132" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D132" s="2" t="inlineStr">
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
         <is>
           <t>Thu, 24 Sep 2026 12:37:44 +0000</t>
         </is>
       </c>
-      <c r="E132" s="2" t="inlineStr">
+      <c r="E130" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F132" s="2" t="inlineStr">
+      <c r="F130" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G132" s="2" t="inlineStr"/>
-      <c r="H132" s="2" t="inlineStr">
+      <c r="G130" s="2" t="inlineStr"/>
+      <c r="H130" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 This title will display on mobile devices
@@ -7172,39 +7097,39 @@
         </is>
       </c>
     </row>
-    <row r="133">
-      <c r="A133" s="2" t="inlineStr">
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B133" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C133" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D133" s="2" t="inlineStr">
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
         <is>
           <t>Mon, 21 Sep 2026 17:07:48 +0000</t>
         </is>
       </c>
-      <c r="E133" s="2" t="inlineStr">
+      <c r="E131" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F133" s="2" t="inlineStr">
+      <c r="F131" s="2" t="inlineStr">
         <is>
           <t>Ver el informe fiscal de China de abril a junio de 2026</t>
         </is>
       </c>
-      <c r="G133" s="2" t="inlineStr"/>
-      <c r="H133" s="2" t="inlineStr">
+      <c r="G131" s="2" t="inlineStr"/>
+      <c r="H131" s="2" t="inlineStr">
         <is>
           <t>96
  Presentamos tu declaración fiscal trimestral a la autoridad tributaria china. Ya puedes descargar la declaración para consultarla.
@@ -7220,39 +7145,39 @@
         </is>
       </c>
     </row>
-    <row r="134">
-      <c r="A134" s="2" t="inlineStr">
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B134" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C134" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D134" s="2" t="inlineStr">
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
         <is>
           <t>Mon, 21 Sep 2026 13:27:57 +0000</t>
         </is>
       </c>
-      <c r="E134" s="2" t="inlineStr">
+      <c r="E132" s="2" t="inlineStr">
         <is>
           <t>Sell with Amazon &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F134" s="2" t="inlineStr">
+      <c r="F132" s="2" t="inlineStr">
         <is>
           <t>Last chance to register for Amazon Accelerate 2026</t>
         </is>
       </c>
-      <c r="G134" s="2" t="inlineStr"/>
-      <c r="H134" s="2" t="inlineStr">
+      <c r="G132" s="2" t="inlineStr"/>
+      <c r="H132" s="2" t="inlineStr">
         <is>
           <t>[Amazon logo](https://go.amazonsellerservices.com/e/229492/2026-09-11/7z5qvbd/6900257597/h/DNy5vrd2KmewvkDHEulcRelQOUFu36-wIzMILRKLzn4)
 [Early-bird ending soon](https://go.amazonsellerservices.com/e/229492/-medium-email-utm-source-email/7z5qvbh/6900257597/h/DNy5vrd2KmewvkDHEulcRelQOUFu36-wIzMILRKLzn4)
@@ -7267,39 +7192,39 @@
         </is>
       </c>
     </row>
-    <row r="135">
-      <c r="A135" s="2" t="inlineStr">
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B135" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C135" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D135" s="2" t="inlineStr">
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
         <is>
           <t>Sun, 20 Sep 2026 14:07:50 +0000</t>
         </is>
       </c>
-      <c r="E135" s="2" t="inlineStr">
+      <c r="E133" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F135" s="2" t="inlineStr">
+      <c r="F133" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G135" s="2" t="inlineStr"/>
-      <c r="H135" s="2" t="inlineStr">
+      <c r="G133" s="2" t="inlineStr"/>
+      <c r="H133" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -7319,39 +7244,39 @@
         </is>
       </c>
     </row>
-    <row r="136">
-      <c r="A136" s="2" t="inlineStr">
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B136" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C136" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D136" s="2" t="inlineStr">
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
         <is>
           <t>Thu, 17 Sep 2026 12:34:14 +0000</t>
         </is>
       </c>
-      <c r="E136" s="2" t="inlineStr">
+      <c r="E134" s="2" t="inlineStr">
         <is>
           <t>Sell with Amazon &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F136" s="2" t="inlineStr">
+      <c r="F134" s="2" t="inlineStr">
         <is>
           <t>Registration closes this Friday—save $200 with your exclusive code</t>
         </is>
       </c>
-      <c r="G136" s="2" t="inlineStr"/>
-      <c r="H136" s="2" t="inlineStr">
+      <c r="G134" s="2" t="inlineStr"/>
+      <c r="H134" s="2" t="inlineStr">
         <is>
           <t>[Amazon logo](https://go.amazonsellerservices.com/e/229492/2026-09-15/7z5szk3/6892578632/h/_CYRbTDGVtA_TsyRgyvyoHjCej_EjJw20h52f6bfhUo)
 [Partner Connect at Accelerate 2026](https://go.amazonsellerservices.com/e/229492/-medium-email-utm-source-email/7z5szk6/6892578632/h/_CYRbTDGVtA_TsyRgyvyoHjCej_EjJw20h52f6bfhUo)
@@ -7365,39 +7290,39 @@
         </is>
       </c>
     </row>
-    <row r="137">
-      <c r="A137" s="2" t="inlineStr">
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B137" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C137" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D137" s="2" t="inlineStr">
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
         <is>
           <t>Wed, 16 Sep 2026 12:07:50 +0000</t>
         </is>
       </c>
-      <c r="E137" s="2" t="inlineStr">
+      <c r="E135" s="2" t="inlineStr">
         <is>
           <t>Sell with Amazon &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F137" s="2" t="inlineStr">
+      <c r="F135" s="2" t="inlineStr">
         <is>
           <t>Strategies built for sellers at your stage—plus $200 off</t>
         </is>
       </c>
-      <c r="G137" s="2" t="inlineStr"/>
-      <c r="H137" s="2" t="inlineStr">
+      <c r="G135" s="2" t="inlineStr"/>
+      <c r="H135" s="2" t="inlineStr">
         <is>
           <t>[Amazon logo](https://go.amazonsellerservices.com/e/229492/2026-09-10/7z5qrvp/6889941143/h/MQuKVqSCTubvlftYjmZsRYwIhpcMmpopXweaNOtgp5c)
 [Secure your spot](https://go.amazonsellerservices.com/e/229492/-medium-email-utm-source-email/7z5qrvs/6889941143/h/MQuKVqSCTubvlftYjmZsRYwIhpcMmpopXweaNOtgp5c)
@@ -7411,39 +7336,39 @@
         </is>
       </c>
     </row>
-    <row r="138">
-      <c r="A138" s="2" t="inlineStr">
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B138" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C138" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D138" s="2" t="inlineStr">
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
         <is>
           <t>Tue, 15 Sep 2026 15:16:31 +0000</t>
         </is>
       </c>
-      <c r="E138" s="2" t="inlineStr">
+      <c r="E136" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F138" s="2" t="inlineStr">
+      <c r="F136" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G138" s="2" t="inlineStr"/>
-      <c r="H138" s="2" t="inlineStr">
+      <c r="G136" s="2" t="inlineStr"/>
+      <c r="H136" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -7463,39 +7388,39 @@
         </is>
       </c>
     </row>
-    <row r="139">
-      <c r="A139" s="2" t="inlineStr">
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B139" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C139" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D139" s="2" t="inlineStr">
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
         <is>
           <t>Tue, 15 Sep 2026 14:49:51 +0000</t>
         </is>
       </c>
-      <c r="E139" s="2" t="inlineStr">
+      <c r="E137" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F139" s="2" t="inlineStr">
+      <c r="F137" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G139" s="2" t="inlineStr"/>
-      <c r="H139" s="2" t="inlineStr">
+      <c r="G137" s="2" t="inlineStr"/>
+      <c r="H137" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -7512,39 +7437,39 @@
         </is>
       </c>
     </row>
-    <row r="140">
-      <c r="A140" s="2" t="inlineStr">
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B140" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C140" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D140" s="2" t="inlineStr">
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
         <is>
           <t>Tue, 15 Sep 2026 13:38:38 +0000</t>
         </is>
       </c>
-      <c r="E140" s="2" t="inlineStr">
+      <c r="E138" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F140" s="2" t="inlineStr">
+      <c r="F138" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G140" s="2" t="inlineStr"/>
-      <c r="H140" s="2" t="inlineStr">
+      <c r="G138" s="2" t="inlineStr"/>
+      <c r="H138" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -7564,39 +7489,39 @@
         </is>
       </c>
     </row>
-    <row r="141">
-      <c r="A141" s="2" t="inlineStr">
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B141" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C141" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D141" s="2" t="inlineStr">
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
         <is>
           <t>Mon, 14 Sep 2026 13:11:23 +0000</t>
         </is>
       </c>
-      <c r="E141" s="2" t="inlineStr">
+      <c r="E139" s="2" t="inlineStr">
         <is>
           <t>Amazon Accelerate &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F141" s="2" t="inlineStr">
+      <c r="F139" s="2" t="inlineStr">
         <is>
           <t>The Accelerate 2026 agenda got even better. See what's new.</t>
         </is>
       </c>
-      <c r="G141" s="2" t="inlineStr"/>
-      <c r="H141" s="2" t="inlineStr">
+      <c r="G139" s="2" t="inlineStr"/>
+      <c r="H139" s="2" t="inlineStr">
         <is>
           <t>[Amazon logo](https://go.amazonsellerservices.com/e/229492/2026-09-04/7z5l4gm/6885907415/h/1g4K0sP-fwBdUvnQHTI9XLWTzXNhSmHYs6__l_Evdwk)
 [Early-bird ending soon](https://go.amazonsellerservices.com/e/229492/-medium-email-utm-source-email/7z5l4gq/6885907415/h/1g4K0sP-fwBdUvnQHTI9XLWTzXNhSmHYs6__l_Evdwk)
@@ -7614,39 +7539,39 @@
         </is>
       </c>
     </row>
-    <row r="142">
-      <c r="A142" s="2" t="inlineStr">
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B142" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C142" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D142" s="2" t="inlineStr">
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
         <is>
           <t>Sat, 12 Sep 2026 00:41:46 +0000</t>
         </is>
       </c>
-      <c r="E142" s="2" t="inlineStr">
+      <c r="E140" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F142" s="2" t="inlineStr">
+      <c r="F140" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G142" s="2" t="inlineStr"/>
-      <c r="H142" s="2" t="inlineStr">
+      <c r="G140" s="2" t="inlineStr"/>
+      <c r="H140" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -7666,39 +7591,39 @@
         </is>
       </c>
     </row>
-    <row r="143">
-      <c r="A143" s="2" t="inlineStr">
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B143" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C143" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D143" s="2" t="inlineStr">
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
         <is>
           <t>Fri, 11 Sep 2026 14:52:08 +0000</t>
         </is>
       </c>
-      <c r="E143" s="2" t="inlineStr">
+      <c r="E141" s="2" t="inlineStr">
         <is>
           <t>Amazon Accelerate &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F143" s="2" t="inlineStr">
+      <c r="F141" s="2" t="inlineStr">
         <is>
           <t>Discover sessions built for growing businesses, and save $200</t>
         </is>
       </c>
-      <c r="G143" s="2" t="inlineStr"/>
-      <c r="H143" s="2" t="inlineStr">
+      <c r="G141" s="2" t="inlineStr"/>
+      <c r="H141" s="2" t="inlineStr">
         <is>
           <t>[Amazon logo](https://go.amazonsellerservices.com/e/229492/2026-09-10/7z5qrws/6883537229/h/8hGIqk3myHUPoHwg1cA2VFOh0rQM9Qk9zX-mp3ce36Q)
 [Partner Connect at Accelerate 2026](https://go.amazonsellerservices.com/e/229492/-medium-email-utm-source-email/7z5qrww/6883537229/h/8hGIqk3myHUPoHwg1cA2VFOh0rQM9Qk9zX-mp3ce36Q)
@@ -7711,39 +7636,39 @@
         </is>
       </c>
     </row>
-    <row r="144">
-      <c r="A144" s="2" t="inlineStr">
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B144" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C144" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D144" s="2" t="inlineStr">
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
         <is>
           <t>Thu, 10 Sep 2026 12:33:05 +0000</t>
         </is>
       </c>
-      <c r="E144" s="2" t="inlineStr">
+      <c r="E142" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F144" s="2" t="inlineStr">
+      <c r="F142" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G144" s="2" t="inlineStr"/>
-      <c r="H144" s="2" t="inlineStr">
+      <c r="G142" s="2" t="inlineStr"/>
+      <c r="H142" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -7763,39 +7688,39 @@
         </is>
       </c>
     </row>
-    <row r="145">
-      <c r="A145" s="2" t="inlineStr">
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B145" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C145" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D145" s="2" t="inlineStr">
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
         <is>
           <t>Thu, 10 Sep 2026 12:27:50 +0000</t>
         </is>
       </c>
-      <c r="E145" s="2" t="inlineStr">
+      <c r="E143" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F145" s="2" t="inlineStr">
+      <c r="F143" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G145" s="2" t="inlineStr"/>
-      <c r="H145" s="2" t="inlineStr">
+      <c r="G143" s="2" t="inlineStr"/>
+      <c r="H143" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -7812,39 +7737,39 @@
         </is>
       </c>
     </row>
-    <row r="146">
-      <c r="A146" s="2" t="inlineStr">
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B146" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C146" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D146" s="2" t="inlineStr">
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
         <is>
           <t>Wed, 9 Sep 2026 14:22:12 +0000</t>
         </is>
       </c>
-      <c r="E146" s="2" t="inlineStr">
+      <c r="E144" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F146" s="2" t="inlineStr">
+      <c r="F144" s="2" t="inlineStr">
         <is>
           <t>Rettifica del saldo negativo nei tuoi account</t>
         </is>
       </c>
-      <c r="G146" s="2" t="inlineStr"/>
-      <c r="H146" s="2" t="inlineStr">
+      <c r="G144" s="2" t="inlineStr"/>
+      <c r="H144" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -7868,39 +7793,39 @@
         </is>
       </c>
     </row>
-    <row r="147">
-      <c r="A147" s="2" t="inlineStr">
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B147" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C147" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D147" s="2" t="inlineStr">
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
         <is>
           <t>Wed, 9 Sep 2026 13:24:25 +0000</t>
         </is>
       </c>
-      <c r="E147" s="2" t="inlineStr">
+      <c r="E145" s="2" t="inlineStr">
         <is>
           <t>Sell with Amazon &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F147" s="2" t="inlineStr">
+      <c r="F145" s="2" t="inlineStr">
         <is>
           <t>New sessions on AI, brand building, and account health</t>
         </is>
       </c>
-      <c r="G147" s="2" t="inlineStr"/>
-      <c r="H147" s="2" t="inlineStr">
+      <c r="G145" s="2" t="inlineStr"/>
+      <c r="H145" s="2" t="inlineStr">
         <is>
           <t>[Amazon logo](https://go.amazonsellerservices.com/e/229492/2026-09-04/7z5l4fj/6879091625/h/N9M90HPlPpU67n4uE_mKTweCIMAyiYf9R4WAB4ShsLU)
 [Early-bird ending soon](https://go.amazonsellerservices.com/e/229492/-medium-email-utm-source-email/7z5l4fm/6879091625/h/N9M90HPlPpU67n4uE_mKTweCIMAyiYf9R4WAB4ShsLU)
@@ -7916,39 +7841,39 @@
         </is>
       </c>
     </row>
-    <row r="148">
-      <c r="A148" s="2" t="inlineStr">
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B148" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C148" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D148" s="2" t="inlineStr">
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
         <is>
           <t>Wed, 30 Sep 2026 10:06:35 +0000</t>
         </is>
       </c>
-      <c r="E148" s="2" t="inlineStr">
+      <c r="E146" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F148" s="2" t="inlineStr">
+      <c r="F146" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G148" s="2" t="inlineStr"/>
-      <c r="H148" s="2" t="inlineStr">
+      <c r="G146" s="2" t="inlineStr"/>
+      <c r="H146" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Submit product safety documentation to reactivate listings
@@ -7966,39 +7891,39 @@
         </is>
       </c>
     </row>
-    <row r="149">
-      <c r="A149" s="2" t="inlineStr">
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B149" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C149" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D149" s="2" t="inlineStr">
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
         <is>
           <t>Tue, 29 Sep 2026 10:06:26 +0000</t>
         </is>
       </c>
-      <c r="E149" s="2" t="inlineStr">
+      <c r="E147" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F149" s="2" t="inlineStr">
+      <c r="F147" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G149" s="2" t="inlineStr"/>
-      <c r="H149" s="2" t="inlineStr">
+      <c r="G147" s="2" t="inlineStr"/>
+      <c r="H147" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Submit product safety documentation to reactivate listings
@@ -8016,39 +7941,39 @@
         </is>
       </c>
     </row>
-    <row r="150">
-      <c r="A150" s="2" t="inlineStr">
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B150" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C150" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D150" s="2" t="inlineStr">
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
         <is>
           <t>Tue, 29 Sep 2026 05:31:39 +0000</t>
         </is>
       </c>
-      <c r="E150" s="2" t="inlineStr">
+      <c r="E148" s="2" t="inlineStr">
         <is>
           <t>亚马逊全球开店 &lt;info@globalselling.amazon.cn&gt;</t>
         </is>
       </c>
-      <c r="F150" s="2" t="inlineStr">
+      <c r="F148" s="2" t="inlineStr">
         <is>
           <t>重要通知｜9月1日起，Pan-EU入库欧盟及直接发往法国的货件必须提供进口详情</t>
         </is>
       </c>
-      <c r="G150" s="2" t="inlineStr"/>
-      <c r="H150" s="2" t="inlineStr">
+      <c r="G148" s="2" t="inlineStr"/>
+      <c r="H148" s="2" t="inlineStr">
         <is>
           <t>未提供 MRN+EORI 将无法创建新货件，请在收货后 60 天内完成补全
 尊敬的 深圳市微海众信科技有限公司,
@@ -8076,39 +8001,39 @@
         </is>
       </c>
     </row>
-    <row r="151">
-      <c r="A151" s="2" t="inlineStr">
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B151" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C151" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D151" s="2" t="inlineStr">
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
         <is>
           <t>Mon, 28 Sep 2026 10:05:46 +0000</t>
         </is>
       </c>
-      <c r="E151" s="2" t="inlineStr">
+      <c r="E149" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F151" s="2" t="inlineStr">
+      <c r="F149" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G151" s="2" t="inlineStr"/>
-      <c r="H151" s="2" t="inlineStr">
+      <c r="G149" s="2" t="inlineStr"/>
+      <c r="H149" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Hello Weihai CA,
@@ -8127,39 +8052,39 @@
         </is>
       </c>
     </row>
-    <row r="152">
-      <c r="A152" s="2" t="inlineStr">
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B152" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C152" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D152" s="2" t="inlineStr">
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
         <is>
           <t>Sun, 27 Sep 2026 10:05:10 +0000</t>
         </is>
       </c>
-      <c r="E152" s="2" t="inlineStr">
+      <c r="E150" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F152" s="2" t="inlineStr">
+      <c r="F150" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G152" s="2" t="inlineStr"/>
-      <c r="H152" s="2" t="inlineStr">
+      <c r="G150" s="2" t="inlineStr"/>
+      <c r="H150" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Hello Weihai CA,
@@ -8178,39 +8103,39 @@
         </is>
       </c>
     </row>
-    <row r="153">
-      <c r="A153" s="2" t="inlineStr">
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B153" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C153" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D153" s="2" t="inlineStr">
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
         <is>
           <t>Sat, 26 Sep 2026 01:10:33 +0000</t>
         </is>
       </c>
-      <c r="E153" s="2" t="inlineStr">
+      <c r="E151" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F153" s="2" t="inlineStr">
+      <c r="F151" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G153" s="2" t="inlineStr"/>
-      <c r="H153" s="2" t="inlineStr">
+      <c r="G151" s="2" t="inlineStr"/>
+      <c r="H151" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -8228,39 +8153,39 @@
         </is>
       </c>
     </row>
-    <row r="154">
-      <c r="A154" s="2" t="inlineStr">
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B154" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C154" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D154" s="2" t="inlineStr">
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
         <is>
           <t>Sat, 26 Sep 2026 01:07:50 +0000</t>
         </is>
       </c>
-      <c r="E154" s="2" t="inlineStr">
+      <c r="E152" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F154" s="2" t="inlineStr">
+      <c r="F152" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G154" s="2" t="inlineStr"/>
-      <c r="H154" s="2" t="inlineStr">
+      <c r="G152" s="2" t="inlineStr"/>
+      <c r="H152" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -8278,39 +8203,39 @@
         </is>
       </c>
     </row>
-    <row r="155">
-      <c r="A155" s="2" t="inlineStr">
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B155" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C155" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D155" s="2" t="inlineStr">
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
         <is>
           <t>Thu, 24 Sep 2026 14:57:06 +0000</t>
         </is>
       </c>
-      <c r="E155" s="2" t="inlineStr">
+      <c r="E153" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F155" s="2" t="inlineStr">
+      <c r="F153" s="2" t="inlineStr">
         <is>
           <t>Zwrot kosztów zgodności z wymogami w zakresie opakowań w ramach ROP</t>
         </is>
       </c>
-      <c r="G155" s="2" t="inlineStr"/>
-      <c r="H155" s="2" t="inlineStr">
+      <c r="G153" s="2" t="inlineStr"/>
+      <c r="H153" s="2" t="inlineStr">
         <is>
           <t>96
  Dokończenie rejestracji w ramach ROP i uzyskanie częściowego zwrotu kosztów w Polsce
@@ -8327,39 +8252,39 @@
         </is>
       </c>
     </row>
-    <row r="156">
-      <c r="A156" s="2" t="inlineStr">
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B156" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C156" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D156" s="2" t="inlineStr">
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
         <is>
           <t>Thu, 24 Sep 2026 14:07:32 +0000</t>
         </is>
       </c>
-      <c r="E156" s="2" t="inlineStr">
+      <c r="E154" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F156" s="2" t="inlineStr">
+      <c r="F154" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G156" s="2" t="inlineStr"/>
-      <c r="H156" s="2" t="inlineStr">
+      <c r="G154" s="2" t="inlineStr"/>
+      <c r="H154" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Submit product safety documentation to reactivate listings
@@ -8377,39 +8302,39 @@
         </is>
       </c>
     </row>
-    <row r="157">
-      <c r="A157" s="2" t="inlineStr">
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B157" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C157" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D157" s="2" t="inlineStr">
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
         <is>
           <t>Thu, 24 Sep 2026 10:28:03 +0000</t>
         </is>
       </c>
-      <c r="E157" s="2" t="inlineStr">
+      <c r="E155" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F157" s="2" t="inlineStr">
+      <c r="F155" s="2" t="inlineStr">
         <is>
           <t>Få ersättning för kostnader för överensstämmelse med EPR-förpackningar</t>
         </is>
       </c>
-      <c r="G157" s="2" t="inlineStr"/>
-      <c r="H157" s="2" t="inlineStr">
+      <c r="G155" s="2" t="inlineStr"/>
+      <c r="H155" s="2" t="inlineStr">
         <is>
           <t>96
  Slutför EPR-registreringen och få en del av kostnaderna återbetalda i Sverige
@@ -8427,39 +8352,39 @@
         </is>
       </c>
     </row>
-    <row r="158">
-      <c r="A158" s="2" t="inlineStr">
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B158" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C158" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D158" s="2" t="inlineStr">
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
         <is>
           <t>Thu, 24 Sep 2026 10:08:29 +0000</t>
         </is>
       </c>
-      <c r="E158" s="2" t="inlineStr">
+      <c r="E156" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F158" s="2" t="inlineStr">
+      <c r="F156" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G158" s="2" t="inlineStr"/>
-      <c r="H158" s="2" t="inlineStr">
+      <c r="G156" s="2" t="inlineStr"/>
+      <c r="H156" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -8478,39 +8403,39 @@
         </is>
       </c>
     </row>
-    <row r="159">
-      <c r="A159" s="2" t="inlineStr">
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B159" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C159" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D159" s="2" t="inlineStr">
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="inlineStr">
         <is>
           <t>Thu, 24 Sep 2026 10:08:17 +0000</t>
         </is>
       </c>
-      <c r="E159" s="2" t="inlineStr">
+      <c r="E157" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F159" s="2" t="inlineStr">
+      <c r="F157" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G159" s="2" t="inlineStr"/>
-      <c r="H159" s="2" t="inlineStr">
+      <c r="G157" s="2" t="inlineStr"/>
+      <c r="H157" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -8529,39 +8454,39 @@
         </is>
       </c>
     </row>
-    <row r="160">
-      <c r="A160" s="2" t="inlineStr">
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B160" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C160" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D160" s="2" t="inlineStr">
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
         <is>
           <t>Tue, 22 Sep 2026 07:40:02 +0000</t>
         </is>
       </c>
-      <c r="E160" s="2" t="inlineStr">
+      <c r="E158" s="2" t="inlineStr">
         <is>
           <t>"pli-cn-seller-compliance@amazon.com" &lt;pli-cn-seller-compliance@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F160" s="2" t="inlineStr">
+      <c r="F158" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 22191892721] [立刻采取行动购买或更新商业责任险]</t>
         </is>
       </c>
-      <c r="G160" s="2" t="inlineStr"/>
-      <c r="H160" s="2" t="inlineStr">
+      <c r="G158" s="2" t="inlineStr"/>
+      <c r="H158" s="2" t="inlineStr">
         <is>
           <t>96
 RE:[CASE 22191892721] [立刻采取行动购买或更新商业责任险]
@@ -8591,39 +8516,39 @@
         </is>
       </c>
     </row>
-    <row r="161">
-      <c r="A161" s="2" t="inlineStr">
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B161" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C161" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D161" s="2" t="inlineStr">
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="inlineStr">
         <is>
           <t>Fri, 18 Sep 2026 15:44:09 +0000</t>
         </is>
       </c>
-      <c r="E161" s="2" t="inlineStr">
+      <c r="E159" s="2" t="inlineStr">
         <is>
           <t>cscompliance-docreview-seller@amazon.de</t>
         </is>
       </c>
-      <c r="F161" s="2" t="inlineStr">
+      <c r="F159" s="2" t="inlineStr">
         <is>
           <t>Problem gelöst (Anfrage Nr.: 13280404852)</t>
         </is>
       </c>
-      <c r="G161" s="2" t="inlineStr"/>
-      <c r="H161" s="2" t="inlineStr">
+      <c r="G159" s="2" t="inlineStr"/>
+      <c r="H159" s="2" t="inlineStr">
         <is>
           <t>96
 Problem gelöst (Anfrage Nr.: 13280404852)
@@ -8645,41 +8570,41 @@
         </is>
       </c>
     </row>
-    <row r="162">
-      <c r="A162" s="2" t="inlineStr">
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B162" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C162" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D162" s="2" t="inlineStr">
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
         <is>
           <t>Fri, 18 Sep 2026 15:42:38 +0000</t>
         </is>
       </c>
-      <c r="E162" s="2" t="inlineStr">
+      <c r="E160" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.de" &lt;cscompliance-docreview-seller@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F162" s="2" t="inlineStr">
+      <c r="F160" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 13280404852] SELLER: A1UYGOR4ZW45MU, ASIN: B0GYPZ58JY,
  MARKETPLACE: A1PA6795UKMFR9 - SPO - Seller Partner Outreach - Document
  Review</t>
         </is>
       </c>
-      <c r="G162" s="2" t="inlineStr"/>
-      <c r="H162" s="2" t="inlineStr">
+      <c r="G160" s="2" t="inlineStr"/>
+      <c r="H160" s="2" t="inlineStr">
         <is>
           <t>96
 RE:[CASE 13280404852] SELLER: A1UYGOR4ZW45MU, ASIN: B0GYPZ58JY, MARKETPLACE: A1PA6795UKMFR9 - SPO - Seller Partner Outreach - Document Review
@@ -8697,40 +8622,40 @@
         </is>
       </c>
     </row>
-    <row r="163">
-      <c r="A163" s="2" t="inlineStr">
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B163" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C163" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D163" s="2" t="inlineStr">
+      <c r="B161" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C161" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="inlineStr">
         <is>
           <t>Fri, 18 Sep 2026 08:56:32 +0000</t>
         </is>
       </c>
-      <c r="E163" s="2" t="inlineStr">
+      <c r="E161" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.de" &lt;cscompliance-docreview-seller@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F163" s="2" t="inlineStr">
+      <c r="F161" s="2" t="inlineStr">
         <is>
           <t>SELLER: A1UYGOR4ZW45MU, ASIN: B0GYPZ58JY, MARKETPLACE:
  A1PA6795UKMFR9 - SPO - Seller Partner Outreach - Document Review</t>
         </is>
       </c>
-      <c r="G163" s="2" t="inlineStr"/>
-      <c r="H163" s="2" t="inlineStr">
+      <c r="G161" s="2" t="inlineStr"/>
+      <c r="H161" s="2" t="inlineStr">
         <is>
           <t>96
 SELLER: A1UYGOR4ZW45MU, ASIN: B0GYPZ58JY, MARKETPLACE: A1PA6795UKMFR9 - SPO - Seller Partner Outreach - Document Review
@@ -8755,39 +8680,39 @@
         </is>
       </c>
     </row>
-    <row r="164">
-      <c r="A164" s="2" t="inlineStr">
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B164" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C164" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D164" s="2" t="inlineStr">
+      <c r="B162" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C162" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D162" s="2" t="inlineStr">
         <is>
           <t>Wed, 16 Sep 2026 07:08:09 +0000</t>
         </is>
       </c>
-      <c r="E164" s="2" t="inlineStr">
+      <c r="E162" s="2" t="inlineStr">
         <is>
           <t>"ppwr-cn-seller-compliance@amazon.com" &lt;ppwr-cn-seller-compliance@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F164" s="2" t="inlineStr">
+      <c r="F162" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 12309992722] 需要采取行动：请向亚马逊提交您的EPR包装法注册号</t>
         </is>
       </c>
-      <c r="G164" s="2" t="inlineStr"/>
-      <c r="H164" s="2" t="inlineStr">
+      <c r="G162" s="2" t="inlineStr"/>
+      <c r="H162" s="2" t="inlineStr">
         <is>
           <t>96
 RE:[CASE 12309992722] 需要采取行动：请向亚马逊提交您的EPR包装法注册号
@@ -8814,40 +8739,40 @@
         </is>
       </c>
     </row>
-    <row r="165">
-      <c r="A165" s="2" t="inlineStr">
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B165" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C165" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D165" s="2" t="inlineStr">
+      <c r="B163" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C163" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D163" s="2" t="inlineStr">
         <is>
           <t>Tue, 15 Sep 2026 20:32:42 +0000</t>
         </is>
       </c>
-      <c r="E165" s="2" t="inlineStr">
+      <c r="E163" s="2" t="inlineStr">
         <is>
           <t>The Amazon Services team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F165" s="2" t="inlineStr">
+      <c r="F163" s="2" t="inlineStr">
         <is>
           <t>Submit proof of insurance by January 18 to avoid listing
  deactivation</t>
         </is>
       </c>
-      <c r="G165" s="2" t="inlineStr"/>
-      <c r="H165" s="2" t="inlineStr">
+      <c r="G163" s="2" t="inlineStr"/>
+      <c r="H163" s="2" t="inlineStr">
         <is>
           <t>96
  Review your impacted products and categories and submit proof of insurance before January 18, 2027 to avoid listing deactivation.
@@ -8863,40 +8788,40 @@
         </is>
       </c>
     </row>
-    <row r="166">
-      <c r="A166" s="2" t="inlineStr">
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B166" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C166" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D166" s="2" t="inlineStr">
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="inlineStr">
         <is>
           <t>Mon, 14 Sep 2026 05:40:35 +0000</t>
         </is>
       </c>
-      <c r="E166" s="2" t="inlineStr">
+      <c r="E164" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.de" &lt;cscompliance-docreview-seller@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F166" s="2" t="inlineStr">
+      <c r="F164" s="2" t="inlineStr">
         <is>
           <t>SELLER: A1UYGOR4ZW45MU, ASIN: B0GYPZ58JY, MARKETPLACE:
  A1PA6795UKMFR9 - SPO - Seller Partner Outreach - Document Review</t>
         </is>
       </c>
-      <c r="G166" s="2" t="inlineStr"/>
-      <c r="H166" s="2" t="inlineStr">
+      <c r="G164" s="2" t="inlineStr"/>
+      <c r="H164" s="2" t="inlineStr">
         <is>
           <t>96
 SELLER: A1UYGOR4ZW45MU, ASIN: B0GYPZ58JY, MARKETPLACE: A1PA6795UKMFR9 - SPO - Seller Partner Outreach - Document Review
@@ -8915,39 +8840,39 @@
         </is>
       </c>
     </row>
-    <row r="167">
-      <c r="A167" s="2" t="inlineStr">
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B167" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C167" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D167" s="2" t="inlineStr">
+      <c r="B165" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C165" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D165" s="2" t="inlineStr">
         <is>
           <t>Thu, 10 Sep 2026 15:50:06 +0000</t>
         </is>
       </c>
-      <c r="E167" s="2" t="inlineStr">
+      <c r="E165" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F167" s="2" t="inlineStr">
+      <c r="F165" s="2" t="inlineStr">
         <is>
           <t>Submit product compliance documents to avoid listing removal</t>
         </is>
       </c>
-      <c r="G167" s="2" t="inlineStr"/>
-      <c r="H167" s="2" t="inlineStr">
+      <c r="G165" s="2" t="inlineStr"/>
+      <c r="H165" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product compliance documents to avoid listing removal
@@ -8969,39 +8894,39 @@
         </is>
       </c>
     </row>
-    <row r="168">
-      <c r="A168" s="2" t="inlineStr">
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B168" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C168" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D168" s="2" t="inlineStr">
+      <c r="B166" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="inlineStr">
         <is>
           <t>Wed, 9 Sep 2026 18:07:39 +0000</t>
         </is>
       </c>
-      <c r="E168" s="2" t="inlineStr">
+      <c r="E166" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F168" s="2" t="inlineStr">
+      <c r="F166" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G168" s="2" t="inlineStr"/>
-      <c r="H168" s="2" t="inlineStr">
+      <c r="G166" s="2" t="inlineStr"/>
+      <c r="H166" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Submit product safety documentation to reactivate listings
@@ -9019,39 +8944,39 @@
         </is>
       </c>
     </row>
-    <row r="169">
-      <c r="A169" s="2" t="inlineStr">
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B169" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C169" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D169" s="2" t="inlineStr">
+      <c r="B167" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C167" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="inlineStr">
         <is>
           <t>Wed, 9 Sep 2026 15:09:01 +0000</t>
         </is>
       </c>
-      <c r="E169" s="2" t="inlineStr">
+      <c r="E167" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F169" s="2" t="inlineStr">
+      <c r="F167" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G169" s="2" t="inlineStr"/>
-      <c r="H169" s="2" t="inlineStr">
+      <c r="G167" s="2" t="inlineStr"/>
+      <c r="H167" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -9069,6 +8994,98 @@
         </is>
       </c>
     </row>
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 2 Oct 2026 08:41:07 +0000</t>
+        </is>
+      </c>
+      <c r="E168" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F168" s="2" t="inlineStr">
+        <is>
+          <t>Zmiana kategorii opłat obowiązująca od 31 października 2026 r.</t>
+        </is>
+      </c>
+      <c r="G168" s="2" t="inlineStr"/>
+      <c r="H168" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">96
+ Zmiana kategorii opłat w przypadku niektórych Twoich produktów w europejskich sklepach Amazon
+ Dzień dobry,
+31 października 2026 r. niektóre Twoje produkty w europejskich sklepach Amazon zostaną przypisane do zaktualizowanych kategorii opłat.
+Kategorie opłat określają, jakim rodzajem produktu jest dany ASIN, przy czym mogą różnić się od kategorii, w których produkty są wystawione w naszych sklepach. Każdy produkt w naszym katalogu może należeć tylko do jednej kategorii opłat. Regularnie sprawdzamy produkty, aby mieć pewność, że zostały przypisane do odpowiednich kategorii opłat zgodnie z naszymi wytycznymi dotyczącymi kategorii opłat .
+To tylko aktualizacja kategorii opłat. Jednak po przypisaniu produktu do nowej kategorii opłaty mogą się zmienić, ponieważ różne kategorie mają różne struktury stawek.
+Aby sprawdzić swoje produkty, których dotyczy ta kwestia, i zaktualizowane stawki, pobierz raport o aktualizacji mojej kategorii opłat . Jeśli do danego ASIN masz przypisanych wiele kodów SKU, zmiany dotyczące kategorii opłat będą miały zastosowanie do wszystkich tych jednostek SKU.
+Aby dowiedzieć się więcej o stawkach opłat, przejdź na stronę Opłaty za sprzedaż na Amazon .
+Więcej </t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 2 Oct 2026 07:57:37 +0000</t>
+        </is>
+      </c>
+      <c r="E169" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F169" s="2" t="inlineStr">
+        <is>
+          <t>Actualización de las categorías de tarifas con entrada en vigor el 31 de octubre de 2026</t>
+        </is>
+      </c>
+      <c r="G169" s="2" t="inlineStr"/>
+      <c r="H169" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Se asignarán algunos de tus ASIN a otra categoría de tarifa en nuestras tiendas europeas.
+ Hola:
+Con entrada en vigor el 31 de octubre de 2026, se asignarán algunos de tus ASIN en nuestras tiendas europeas a categorías de tarifas actualizadas.
+Las categorías de tarifas describen qué tipo de producto es un ASIN y pueden ser diferentes de la categoría en la que aparece el ASIN en nuestras tiendas. Cada ASIN de nuestro catálogo sólo puede pertenecer a una única categoría de tarifas. De forma periódica, revisamos los ASIN para asegurarnos de que tengan asignadas las categorías de tarifas correctas, tal y como se muestra en nuestras directrices de las categorías de tarifas .
+Sólo hemos actualizado las categorías de tarifas. Sin embargo, tus tarifas pueden variar cuando se asigne tu ASIN a una categoría nueva, ya que cada categoría tiene una estructura de tarifas distinta.
+Para consultar los ASIN afectados y sus tarifas actualizadas, descarga el Informe de actualización de categorías de tarifas . Si tienes varios SKU para el mismo ASIN, los cambios de categoría se aplicarán a todos los SKU.
+Para más información sobre las tarifas, consulta Tabla de tarifas de Vender en Amazon .
+Para m</t>
+        </is>
+      </c>
+    </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
@@ -9087,21 +9104,111 @@
       </c>
       <c r="D170" s="2" t="inlineStr">
         <is>
-          <t>Thu, 1 Oct 2026 02:30:17 +0000</t>
+          <t>Fri, 2 Oct 2026 07:49:32 +0000</t>
         </is>
       </c>
       <c r="E170" s="2" t="inlineStr">
         <is>
-          <t>"donotreply@amazon.com" &lt;donotreply@amazon.com&gt;</t>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
       <c r="F170" s="2" t="inlineStr">
         <is>
-          <t>Transparency Invoice/Credit note for 09/2026</t>
+          <t>Categorie di commissioni aggiornate dal 31 ottobre 2026</t>
         </is>
       </c>
       <c r="G170" s="2" t="inlineStr"/>
       <c r="H170" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Alcuni dei tuoi ASIN verranno assegnati a una categoria di commissioni diversa nei nostri negozi europei
+ Buongiorno,
+A partire dal 31 ottobre 2026, alcuni dei tuoi ASIN nei nostri negozi europei verranno assegnati a categorie di commissioni aggiornate.
+Le categorie di commissioni descrivono la tipologia di prodotto degli ASIN e possono essere diverse dalle categorie sotto alle quali gli stessi ASIN compaiono nei negozi Amazon. Ogni ASIN presente nel nostro catalogo può appartenere a una sola categoria di commissioni. Verifichiamo regolarmente gli ASIN per garantire che siano assegnati alle categorie di commissioni corrette, come indicato nelle nostre linee guida sulle categorie di commissioni .
+Questo aggiornamento riguarda esclusivamente le categorie di commissioni. Tuttavia, le tue commissioni potrebbero variare quando l'ASIN viene assegnato a una nuova categoria, perché categorie diverse prevedono strutture tariffarie diverse.
+Per consultare gli ASIN interessati e i relativi costi aggiornati, scarica il tuo report sulle modifiche alle categorie di tariffe e commissioni . Se disponi di più SKU per lo stesso ASIN, queste modifiche saranno applicate a tutti gli SKU.
+Per maggio</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 2 Oct 2026 07:46:36 +0000</t>
+        </is>
+      </c>
+      <c r="E171" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F171" s="2" t="inlineStr">
+        <is>
+          <t>Update van kostencategorieën, met ingang van 31 oktober 2026</t>
+        </is>
+      </c>
+      <c r="G171" s="2" t="inlineStr"/>
+      <c r="H171" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Enkele van je ASIN-codes worden toegewezen aan een andere kostencategorie in onze Europese winkels
+ Hallo,
+Met ingang van 31 oktober 2026 worden enkele van jouw ASIN-codes in onze Europese winkels toegewezen aan bijgewerkte kostencategorieën.
+Kostencategorieën beschrijven wat voor soort product een ASIN is en kunnen verschillen van de categorie waarin het ASIN in onze winkels wordt weergegeven. Elk ASIN in onze catalogus kan tot slechts één kostencategorie behoren. We controleren regelmatig ASIN-codes om er zeker van te zijn dat ze aan de juiste kostencategorieën toegewezen zijn, zoals weergegeven in onze Richtlijnen voor kostencategorieën .
+Dit is alleen een update van de kostencategorie. Je kosten kunnen echter verschillen als je ASIN wordt toegewezen aan een nieuwe categorie omdat verschillende categorieën verschillende tariefstructuren hebben.
+Download Mijn overzicht van wijzigingen van kostencategorie om je betreffende ASIN-codes en hun bijgewerkte tarieven te bekijken. Als je meerdere SKU-codes hebt voor hetzelfde ASIN, zijn categoriewijzigingen van toepassing op alle SKU-codes.
+Ga naar het Kostenoverzicht voor Verkopen via Amazon voor meer informatie over kostentarieven.</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B172" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C172" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 1 Oct 2026 02:30:17 +0000</t>
+        </is>
+      </c>
+      <c r="E172" s="2" t="inlineStr">
+        <is>
+          <t>"donotreply@amazon.com" &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F172" s="2" t="inlineStr">
+        <is>
+          <t>Transparency Invoice/Credit note for 09/2026</t>
+        </is>
+      </c>
+      <c r="G172" s="2" t="inlineStr"/>
+      <c r="H172" s="2" t="inlineStr">
         <is>
           <t>96
  Dear Customer,
@@ -9119,39 +9226,39 @@
         </is>
       </c>
     </row>
-    <row r="171">
-      <c r="A171" s="2" t="inlineStr">
+    <row r="173">
+      <c r="A173" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B171" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C171" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D171" s="2" t="inlineStr">
+      <c r="B173" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="inlineStr">
         <is>
           <t>Wed, 30 Sep 2026 08:58:18 +0000</t>
         </is>
       </c>
-      <c r="E171" s="2" t="inlineStr">
+      <c r="E173" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F171" s="2" t="inlineStr">
+      <c r="F173" s="2" t="inlineStr">
         <is>
           <t>You’ve been enrolled in EPR Pay on Behalf for Amazon.co.uk</t>
         </is>
       </c>
-      <c r="G171" s="2" t="inlineStr"/>
-      <c r="H171" s="2" t="inlineStr">
+      <c r="G173" s="2" t="inlineStr"/>
+      <c r="H173" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">You’ve been enrolled in EPR Pay on Behalf for Amazon.co.uk
  96
@@ -9161,39 +9268,39 @@
         </is>
       </c>
     </row>
-    <row r="172">
-      <c r="A172" s="2" t="inlineStr">
+    <row r="174">
+      <c r="A174" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B172" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C172" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D172" s="2" t="inlineStr">
+      <c r="B174" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C174" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="inlineStr">
         <is>
           <t>Mon, 28 Sep 2026 05:54:05 +0000</t>
         </is>
       </c>
-      <c r="E172" s="2" t="inlineStr">
+      <c r="E174" s="2" t="inlineStr">
         <is>
           <t>Transparency No Reply &lt;noreply-transparency@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F172" s="2" t="inlineStr">
+      <c r="F174" s="2" t="inlineStr">
         <is>
           <t>OPR 体验优化——无需再手动追踪货件  /  Improvement to Your OPR Experience — No More Manual Shipment Tracking</t>
         </is>
       </c>
-      <c r="G172" s="2" t="inlineStr"/>
-      <c r="H172" s="2" t="inlineStr">
+      <c r="G174" s="2" t="inlineStr"/>
+      <c r="H174" s="2" t="inlineStr">
         <is>
           <t>尊敬的 Mzyxxel 团队：
 我们很高兴地通知您，OPR（Operational Performance Review运营表现评估）流程迎来一项优化，这将使开启 OPR 变得更加简单，并且您无需再手动追踪货件。
@@ -9217,39 +9324,39 @@
         </is>
       </c>
     </row>
-    <row r="173">
-      <c r="A173" s="2" t="inlineStr">
+    <row r="175">
+      <c r="A175" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B173" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C173" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D173" s="2" t="inlineStr">
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="inlineStr">
         <is>
           <t>Sat, 26 Sep 2026 01:10:17 +0000</t>
         </is>
       </c>
-      <c r="E173" s="2" t="inlineStr">
+      <c r="E175" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F173" s="2" t="inlineStr">
+      <c r="F175" s="2" t="inlineStr">
         <is>
           <t>Presenta la documentación sobre seguridad del producto para reactivar los listings</t>
         </is>
       </c>
-      <c r="G173" s="2" t="inlineStr"/>
-      <c r="H173" s="2" t="inlineStr">
+      <c r="G175" s="2" t="inlineStr"/>
+      <c r="H175" s="2" t="inlineStr">
         <is>
           <t>96
  Presenta la documentación sobre seguridad del producto para reactivar los listings
@@ -9265,40 +9372,40 @@
         </is>
       </c>
     </row>
-    <row r="174">
-      <c r="A174" s="2" t="inlineStr">
+    <row r="176">
+      <c r="A176" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B174" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C174" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D174" s="2" t="inlineStr">
+      <c r="B176" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C176" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D176" s="2" t="inlineStr">
         <is>
           <t>Sat, 26 Sep 2026 01:09:41 +0000</t>
         </is>
       </c>
-      <c r="E174" s="2" t="inlineStr">
+      <c r="E176" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F174" s="2" t="inlineStr">
+      <c r="F176" s="2" t="inlineStr">
         <is>
           <t>Invia la documentazione sulla sicurezza del prodotto per riattivare
  le offerte</t>
         </is>
       </c>
-      <c r="G174" s="2" t="inlineStr"/>
-      <c r="H174" s="2" t="inlineStr">
+      <c r="G176" s="2" t="inlineStr"/>
+      <c r="H176" s="2" t="inlineStr">
         <is>
           <t>96
  Invia la documentazione sulla sicurezza del prodotto per riattivare le offerte
@@ -9314,39 +9421,39 @@
         </is>
       </c>
     </row>
-    <row r="175">
-      <c r="A175" s="2" t="inlineStr">
+    <row r="177">
+      <c r="A177" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B175" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C175" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D175" s="2" t="inlineStr">
+      <c r="B177" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C177" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D177" s="2" t="inlineStr">
         <is>
           <t>Sat, 26 Sep 2026 01:09:40 +0000</t>
         </is>
       </c>
-      <c r="E175" s="2" t="inlineStr">
+      <c r="E177" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F175" s="2" t="inlineStr">
+      <c r="F177" s="2" t="inlineStr">
         <is>
           <t>Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert</t>
         </is>
       </c>
-      <c r="G175" s="2" t="inlineStr"/>
-      <c r="H175" s="2" t="inlineStr">
+      <c r="G177" s="2" t="inlineStr"/>
+      <c r="H177" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert
@@ -9360,40 +9467,40 @@
         </is>
       </c>
     </row>
-    <row r="176">
-      <c r="A176" s="2" t="inlineStr">
+    <row r="178">
+      <c r="A178" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B176" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C176" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D176" s="2" t="inlineStr">
+      <c r="B178" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C178" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D178" s="2" t="inlineStr">
         <is>
           <t>Sat, 26 Sep 2026 01:09:39 +0000</t>
         </is>
       </c>
-      <c r="E176" s="2" t="inlineStr">
+      <c r="E178" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F176" s="2" t="inlineStr">
+      <c r="F178" s="2" t="inlineStr">
         <is>
           <t>Dien productveiligheidsdocumentatie in om productvermeldingen
  opnieuw te activeren</t>
         </is>
       </c>
-      <c r="G176" s="2" t="inlineStr"/>
-      <c r="H176" s="2" t="inlineStr">
+      <c r="G178" s="2" t="inlineStr"/>
+      <c r="H178" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Dien productveiligheidsdocumentatie in om productvermeldingen opnieuw te activeren
@@ -9409,39 +9516,39 @@
         </is>
       </c>
     </row>
-    <row r="177">
-      <c r="A177" s="2" t="inlineStr">
+    <row r="179">
+      <c r="A179" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B177" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C177" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D177" s="2" t="inlineStr">
+      <c r="B179" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C179" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D179" s="2" t="inlineStr">
         <is>
           <t>Sat, 26 Sep 2026 01:09:28 +0000</t>
         </is>
       </c>
-      <c r="E177" s="2" t="inlineStr">
+      <c r="E179" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F177" s="2" t="inlineStr">
+      <c r="F179" s="2" t="inlineStr">
         <is>
           <t>Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter</t>
         </is>
       </c>
-      <c r="G177" s="2" t="inlineStr"/>
-      <c r="H177" s="2" t="inlineStr">
+      <c r="G179" s="2" t="inlineStr"/>
+      <c r="H179" s="2" t="inlineStr">
         <is>
           <t>96
  Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter
@@ -9457,39 +9564,39 @@
         </is>
       </c>
     </row>
-    <row r="178">
-      <c r="A178" s="2" t="inlineStr">
+    <row r="180">
+      <c r="A180" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B178" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C178" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D178" s="2" t="inlineStr">
+      <c r="B180" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C180" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D180" s="2" t="inlineStr">
         <is>
           <t>Sat, 26 Sep 2026 01:08:10 +0000</t>
         </is>
       </c>
-      <c r="E178" s="2" t="inlineStr">
+      <c r="E180" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F178" s="2" t="inlineStr">
+      <c r="F180" s="2" t="inlineStr">
         <is>
           <t>Soumettre la documentation de sécurité des produits pour réactiver les mises en vente</t>
         </is>
       </c>
-      <c r="G178" s="2" t="inlineStr"/>
-      <c r="H178" s="2" t="inlineStr">
+      <c r="G180" s="2" t="inlineStr"/>
+      <c r="H180" s="2" t="inlineStr">
         <is>
           <t>96
  Soumettre la documentation de sécurité des produits pour réactiver les mises en vente
@@ -9505,39 +9612,39 @@
         </is>
       </c>
     </row>
-    <row r="179">
-      <c r="A179" s="2" t="inlineStr">
+    <row r="181">
+      <c r="A181" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B179" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C179" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D179" s="2" t="inlineStr">
+      <c r="B181" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C181" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D181" s="2" t="inlineStr">
         <is>
           <t>Sat, 26 Sep 2026 00:44:41 +0000</t>
         </is>
       </c>
-      <c r="E179" s="2" t="inlineStr">
+      <c r="E181" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F179" s="2" t="inlineStr">
+      <c r="F181" s="2" t="inlineStr">
         <is>
           <t>Votre paiement est en cours</t>
         </is>
       </c>
-      <c r="G179" s="2" t="inlineStr"/>
-      <c r="H179" s="2" t="inlineStr">
+      <c r="G181" s="2" t="inlineStr"/>
+      <c r="H181" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 This title will display on mobile devices
@@ -9553,39 +9660,39 @@
         </is>
       </c>
     </row>
-    <row r="180">
-      <c r="A180" s="2" t="inlineStr">
+    <row r="182">
+      <c r="A182" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B180" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C180" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D180" s="2" t="inlineStr">
+      <c r="B182" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C182" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D182" s="2" t="inlineStr">
         <is>
           <t>Fri, 25 Sep 2026 05:15:49 +0000</t>
         </is>
       </c>
-      <c r="E180" s="2" t="inlineStr">
+      <c r="E182" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F180" s="2" t="inlineStr">
+      <c r="F182" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G180" s="2" t="inlineStr"/>
-      <c r="H180" s="2" t="inlineStr">
+      <c r="G182" s="2" t="inlineStr"/>
+      <c r="H182" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 145 PCS Eisenbahn Elektrisch Cube Track, 3D Schwerkrafttrotzendes Zug Set, DIY Zugstrecken Spielzeug, STEM Lernspielzeug &amp;amp; Geschenkidee für Kinder 3–8 Jahre, Kreatives Bauen Spielzeug
@@ -9606,39 +9713,39 @@
         </is>
       </c>
     </row>
-    <row r="181">
-      <c r="A181" s="2" t="inlineStr">
+    <row r="183">
+      <c r="A183" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B181" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C181" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D181" s="2" t="inlineStr">
+      <c r="B183" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C183" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D183" s="2" t="inlineStr">
         <is>
           <t>Thu, 24 Sep 2026 14:31:24 +0000</t>
         </is>
       </c>
-      <c r="E181" s="2" t="inlineStr">
+      <c r="E183" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Newsletter &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F181" s="2" t="inlineStr">
+      <c r="F183" s="2" t="inlineStr">
         <is>
           <t>Seller News: September 2026</t>
         </is>
       </c>
-      <c r="G181" s="2" t="inlineStr"/>
-      <c r="H181" s="2" t="inlineStr">
+      <c r="G183" s="2" t="inlineStr"/>
+      <c r="H183" s="2" t="inlineStr">
         <is>
           <t>Seller News: September 2026
  96
@@ -9648,39 +9755,39 @@
         </is>
       </c>
     </row>
-    <row r="182">
-      <c r="A182" s="2" t="inlineStr">
+    <row r="184">
+      <c r="A184" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B182" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C182" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D182" s="2" t="inlineStr">
+      <c r="B184" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C184" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D184" s="2" t="inlineStr">
         <is>
           <t>Thu, 24 Sep 2026 09:39:36 +0000</t>
         </is>
       </c>
-      <c r="E182" s="2" t="inlineStr">
+      <c r="E184" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F182" s="2" t="inlineStr">
+      <c r="F184" s="2" t="inlineStr">
         <is>
           <t>Seller News: September 2026</t>
         </is>
       </c>
-      <c r="G182" s="2" t="inlineStr"/>
-      <c r="H182" s="2" t="inlineStr">
+      <c r="G184" s="2" t="inlineStr"/>
+      <c r="H184" s="2" t="inlineStr">
         <is>
           <t>Seller News: September 2026
  96
@@ -9690,39 +9797,39 @@
         </is>
       </c>
     </row>
-    <row r="183">
-      <c r="A183" s="2" t="inlineStr">
+    <row r="185">
+      <c r="A185" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B183" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C183" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D183" s="2" t="inlineStr">
+      <c r="B185" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C185" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D185" s="2" t="inlineStr">
         <is>
           <t>Thu, 24 Sep 2026 05:03:27 +0000</t>
         </is>
       </c>
-      <c r="E183" s="2" t="inlineStr">
+      <c r="E185" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F183" s="2" t="inlineStr">
+      <c r="F185" s="2" t="inlineStr">
         <is>
           <t>Manage returns with rules, not one-offs</t>
         </is>
       </c>
-      <c r="G183" s="2" t="inlineStr"/>
-      <c r="H183" s="2" t="inlineStr">
+      <c r="G185" s="2" t="inlineStr"/>
+      <c r="H185" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Automate return decisions so you're not handling each one manually.
@@ -9744,39 +9851,39 @@
         </is>
       </c>
     </row>
-    <row r="184">
-      <c r="A184" s="2" t="inlineStr">
+    <row r="186">
+      <c r="A186" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B184" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C184" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D184" s="2" t="inlineStr">
+      <c r="B186" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C186" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D186" s="2" t="inlineStr">
         <is>
           <t>Thu, 24 Sep 2026 00:32:28 +0000</t>
         </is>
       </c>
-      <c r="E184" s="2" t="inlineStr">
+      <c r="E186" s="2" t="inlineStr">
         <is>
           <t>亚马逊卖家平台通知 &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F184" s="2" t="inlineStr">
+      <c r="F186" s="2" t="inlineStr">
         <is>
           <t>解决定价错误以重新启售停售商品</t>
         </is>
       </c>
-      <c r="G184" s="2" t="inlineStr"/>
-      <c r="H184" s="2" t="inlineStr">
+      <c r="G186" s="2" t="inlineStr"/>
+      <c r="H186" s="2" t="inlineStr">
         <is>
           <t>96
  因错价而被禁止显示
@@ -9814,39 +9921,39 @@
         </is>
       </c>
     </row>
-    <row r="185">
-      <c r="A185" s="2" t="inlineStr">
+    <row r="187">
+      <c r="A187" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B185" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C185" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D185" s="2" t="inlineStr">
+      <c r="B187" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C187" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D187" s="2" t="inlineStr">
         <is>
           <t>Wed, 23 Sep 2026 14:10:37 +0000</t>
         </is>
       </c>
-      <c r="E185" s="2" t="inlineStr">
+      <c r="E187" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F185" s="2" t="inlineStr">
+      <c r="F187" s="2" t="inlineStr">
         <is>
           <t>Pagamento elaborato con successo</t>
         </is>
       </c>
-      <c r="G185" s="2" t="inlineStr"/>
-      <c r="H185" s="2" t="inlineStr">
+      <c r="G187" s="2" t="inlineStr"/>
+      <c r="H187" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -9861,39 +9968,39 @@
         </is>
       </c>
     </row>
-    <row r="186">
-      <c r="A186" s="2" t="inlineStr">
+    <row r="188">
+      <c r="A188" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B186" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C186" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D186" s="2" t="inlineStr">
+      <c r="B188" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C188" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D188" s="2" t="inlineStr">
         <is>
           <t>Wed, 23 Sep 2026 01:51:02 +0000</t>
         </is>
       </c>
-      <c r="E186" s="2" t="inlineStr">
+      <c r="E188" s="2" t="inlineStr">
         <is>
           <t>Notificaciones de Seller Central (sin buzón electrónico) &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F186" s="2" t="inlineStr">
+      <c r="F188" s="2" t="inlineStr">
         <is>
           <t>Actualización de estado de mercancías peligrosas</t>
         </is>
       </c>
-      <c r="G186" s="2" t="inlineStr"/>
-      <c r="H186" s="2" t="inlineStr">
+      <c r="G188" s="2" t="inlineStr"/>
+      <c r="H188" s="2" t="inlineStr">
         <is>
           <t>96
  Actualización de estado de mercancías peligrosas
@@ -9913,39 +10020,39 @@
         </is>
       </c>
     </row>
-    <row r="187">
-      <c r="A187" s="2" t="inlineStr">
+    <row r="189">
+      <c r="A189" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B187" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C187" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D187" s="2" t="inlineStr">
+      <c r="B189" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C189" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D189" s="2" t="inlineStr">
         <is>
           <t>Wed, 23 Sep 2026 01:45:44 +0000</t>
         </is>
       </c>
-      <c r="E187" s="2" t="inlineStr">
+      <c r="E189" s="2" t="inlineStr">
         <is>
           <t>"Powiadomienia z Amazon Seller Central (nie odpowiadaj)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F187" s="2" t="inlineStr">
+      <c r="F189" s="2" t="inlineStr">
         <is>
           <t>Status materiałów niebezpiecznych (hazmat)</t>
         </is>
       </c>
-      <c r="G187" s="2" t="inlineStr"/>
-      <c r="H187" s="2" t="inlineStr">
+      <c r="G189" s="2" t="inlineStr"/>
+      <c r="H189" s="2" t="inlineStr">
         <is>
           <t>96
  Status materiałów niebezpiecznych (hazmat)
@@ -9965,39 +10072,39 @@
         </is>
       </c>
     </row>
-    <row r="188">
-      <c r="A188" s="2" t="inlineStr">
+    <row r="190">
+      <c r="A190" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B188" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C188" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D188" s="2" t="inlineStr">
+      <c r="B190" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C190" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D190" s="2" t="inlineStr">
         <is>
           <t>Wed, 23 Sep 2026 01:03:52 +0000</t>
         </is>
       </c>
-      <c r="E188" s="2" t="inlineStr">
+      <c r="E190" s="2" t="inlineStr">
         <is>
           <t>"Notifiche di Amazon Seller Central (non rispondere)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F188" s="2" t="inlineStr">
+      <c r="F190" s="2" t="inlineStr">
         <is>
           <t>Aggiornamento dello stato delle merci pericolose</t>
         </is>
       </c>
-      <c r="G188" s="2" t="inlineStr"/>
-      <c r="H188" s="2" t="inlineStr">
+      <c r="G190" s="2" t="inlineStr"/>
+      <c r="H190" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Aggiornamento dello stato delle merci pericolose
@@ -10018,40 +10125,40 @@
         </is>
       </c>
     </row>
-    <row r="189">
-      <c r="A189" s="2" t="inlineStr">
+    <row r="191">
+      <c r="A191" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B189" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C189" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D189" s="2" t="inlineStr">
+      <c r="B191" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C191" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D191" s="2" t="inlineStr">
         <is>
           <t>Tue, 22 Sep 2026 14:20:24 +0000</t>
         </is>
       </c>
-      <c r="E189" s="2" t="inlineStr">
+      <c r="E191" s="2" t="inlineStr">
         <is>
           <t>Notificaciones de Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F189" s="2" t="inlineStr">
+      <c r="F191" s="2" t="inlineStr">
         <is>
           <t>Soluciona los errores de precio para restablecer los listings
  desactivados.</t>
         </is>
       </c>
-      <c r="G189" s="2" t="inlineStr"/>
-      <c r="H189" s="2" t="inlineStr">
+      <c r="G191" s="2" t="inlineStr"/>
+      <c r="H191" s="2" t="inlineStr">
         <is>
           <t>96
  Eliminar errores de precio
@@ -10072,39 +10179,39 @@
         </is>
       </c>
     </row>
-    <row r="190">
-      <c r="A190" s="2" t="inlineStr">
+    <row r="192">
+      <c r="A192" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B190" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C190" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D190" s="2" t="inlineStr">
+      <c r="B192" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C192" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D192" s="2" t="inlineStr">
         <is>
           <t>Tue, 22 Sep 2026 13:01:08 +0000</t>
         </is>
       </c>
-      <c r="E190" s="2" t="inlineStr">
+      <c r="E192" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F190" s="2" t="inlineStr">
+      <c r="F192" s="2" t="inlineStr">
         <is>
           <t>【最后机会】9月23日前提交Prime 会员大促活动</t>
         </is>
       </c>
-      <c r="G190" s="2" t="inlineStr"/>
-      <c r="H190" s="2" t="inlineStr">
+      <c r="G192" s="2" t="inlineStr"/>
+      <c r="H192" s="2" t="inlineStr">
         <is>
           <t>最大化您的 Q4 业绩
 尊敬的卖家，
@@ -10136,39 +10243,39 @@
         </is>
       </c>
     </row>
-    <row r="191">
-      <c r="A191" s="2" t="inlineStr">
+    <row r="193">
+      <c r="A193" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B191" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C191" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D191" s="2" t="inlineStr">
+      <c r="B193" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C193" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D193" s="2" t="inlineStr">
         <is>
           <t>Sun, 20 Sep 2026 15:02:02 +0000</t>
         </is>
       </c>
-      <c r="E191" s="2" t="inlineStr">
+      <c r="E193" s="2" t="inlineStr">
         <is>
           <t>Support Vendeur Amazon &lt;merch.service05@amazon.fr&gt;</t>
         </is>
       </c>
-      <c r="F191" s="2" t="inlineStr">
+      <c r="F193" s="2" t="inlineStr">
         <is>
           <t>&lt;p&gt;Merci d'avoir créé un nouveau Cas: -- 13291403212&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="G191" s="2" t="inlineStr"/>
-      <c r="H191" s="2" t="inlineStr">
+      <c r="G193" s="2" t="inlineStr"/>
+      <c r="H193" s="2" t="inlineStr">
         <is>
           <t>96
 &lt;p&gt;Merci d'avoir créé un nouveau Cas: -- 13291403212&lt;/p&gt;
@@ -10183,39 +10290,39 @@
         </is>
       </c>
     </row>
-    <row r="192">
-      <c r="A192" s="2" t="inlineStr">
+    <row r="194">
+      <c r="A194" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B192" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C192" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D192" s="2" t="inlineStr">
+      <c r="B194" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C194" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D194" s="2" t="inlineStr">
         <is>
           <t>Fri, 18 Sep 2026 16:29:22 +0000</t>
         </is>
       </c>
-      <c r="E192" s="2" t="inlineStr">
+      <c r="E194" s="2" t="inlineStr">
         <is>
           <t>Support Vendeur Amazon &lt;merch.service05@amazon.fr&gt;</t>
         </is>
       </c>
-      <c r="F192" s="2" t="inlineStr">
+      <c r="F194" s="2" t="inlineStr">
         <is>
           <t>&lt;p&gt;Merci d'avoir créé un nouveau Cas: -- 13289094602&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="G192" s="2" t="inlineStr"/>
-      <c r="H192" s="2" t="inlineStr">
+      <c r="G194" s="2" t="inlineStr"/>
+      <c r="H194" s="2" t="inlineStr">
         <is>
           <t>96
 &lt;p&gt;Merci d'avoir créé un nouveau Cas: -- 13289094602&lt;/p&gt;
@@ -10230,39 +10337,39 @@
         </is>
       </c>
     </row>
-    <row r="193">
-      <c r="A193" s="2" t="inlineStr">
+    <row r="195">
+      <c r="A195" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B193" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C193" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D193" s="2" t="inlineStr">
+      <c r="B195" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C195" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D195" s="2" t="inlineStr">
         <is>
           <t>Wed, 16 Sep 2026 01:36:30 +0000</t>
         </is>
       </c>
-      <c r="E193" s="2" t="inlineStr">
+      <c r="E195" s="2" t="inlineStr">
         <is>
           <t>Notificaciones de Seller Central (sin buzón electrónico) &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F193" s="2" t="inlineStr">
+      <c r="F195" s="2" t="inlineStr">
         <is>
           <t>Actualización de estado de mercancías peligrosas</t>
         </is>
       </c>
-      <c r="G193" s="2" t="inlineStr"/>
-      <c r="H193" s="2" t="inlineStr">
+      <c r="G195" s="2" t="inlineStr"/>
+      <c r="H195" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Actualización de estado de mercancías peligrosas
@@ -10285,39 +10392,39 @@
         </is>
       </c>
     </row>
-    <row r="194">
-      <c r="A194" s="2" t="inlineStr">
+    <row r="196">
+      <c r="A196" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B194" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C194" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D194" s="2" t="inlineStr">
+      <c r="B196" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C196" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D196" s="2" t="inlineStr">
         <is>
           <t>Wed, 16 Sep 2026 01:32:49 +0000</t>
         </is>
       </c>
-      <c r="E194" s="2" t="inlineStr">
+      <c r="E196" s="2" t="inlineStr">
         <is>
           <t>"Powiadomienia z Amazon Seller Central (nie odpowiadaj)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F194" s="2" t="inlineStr">
+      <c r="F196" s="2" t="inlineStr">
         <is>
           <t>Status materiałów niebezpiecznych (hazmat)</t>
         </is>
       </c>
-      <c r="G194" s="2" t="inlineStr"/>
-      <c r="H194" s="2" t="inlineStr">
+      <c r="G196" s="2" t="inlineStr"/>
+      <c r="H196" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Status materiałów niebezpiecznych (hazmat)
@@ -10340,39 +10447,39 @@
         </is>
       </c>
     </row>
-    <row r="195">
-      <c r="A195" s="2" t="inlineStr">
+    <row r="197">
+      <c r="A197" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B195" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C195" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D195" s="2" t="inlineStr">
+      <c r="B197" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C197" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D197" s="2" t="inlineStr">
         <is>
           <t>Wed, 16 Sep 2026 01:02:50 +0000</t>
         </is>
       </c>
-      <c r="E195" s="2" t="inlineStr">
+      <c r="E197" s="2" t="inlineStr">
         <is>
           <t>"Notifiche di Amazon Seller Central (non rispondere)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F195" s="2" t="inlineStr">
+      <c r="F197" s="2" t="inlineStr">
         <is>
           <t>Aggiornamento dello stato delle merci pericolose</t>
         </is>
       </c>
-      <c r="G195" s="2" t="inlineStr"/>
-      <c r="H195" s="2" t="inlineStr">
+      <c r="G197" s="2" t="inlineStr"/>
+      <c r="H197" s="2" t="inlineStr">
         <is>
           <t>96
  Aggiornamento dello stato delle merci pericolose
@@ -10395,39 +10502,39 @@
         </is>
       </c>
     </row>
-    <row r="196">
-      <c r="A196" s="2" t="inlineStr">
+    <row r="198">
+      <c r="A198" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B196" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C196" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D196" s="2" t="inlineStr">
+      <c r="B198" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C198" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D198" s="2" t="inlineStr">
         <is>
           <t>Tue, 15 Sep 2026 19:03:56 +0000</t>
         </is>
       </c>
-      <c r="E196" s="2" t="inlineStr">
+      <c r="E198" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F196" s="2" t="inlineStr">
+      <c r="F198" s="2" t="inlineStr">
         <is>
           <t>Recover between 60-80%* from returns</t>
         </is>
       </c>
-      <c r="G196" s="2" t="inlineStr"/>
-      <c r="H196" s="2" t="inlineStr">
+      <c r="G198" s="2" t="inlineStr"/>
+      <c r="H198" s="2" t="inlineStr">
         <is>
           <t>96
  We handle the grading and reselling. You keep control of pricing and recover value.
@@ -10450,39 +10557,39 @@
         </is>
       </c>
     </row>
-    <row r="197">
-      <c r="A197" s="2" t="inlineStr">
+    <row r="199">
+      <c r="A199" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B197" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C197" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D197" s="2" t="inlineStr">
+      <c r="B199" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C199" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D199" s="2" t="inlineStr">
         <is>
           <t>Tue, 15 Sep 2026 15:54:49 +0000</t>
         </is>
       </c>
-      <c r="E197" s="2" t="inlineStr">
+      <c r="E199" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F197" s="2" t="inlineStr">
+      <c r="F199" s="2" t="inlineStr">
         <is>
           <t>Parcel Tax for Austrian B2C orders</t>
         </is>
       </c>
-      <c r="G197" s="2" t="inlineStr"/>
-      <c r="H197" s="2" t="inlineStr">
+      <c r="G199" s="2" t="inlineStr"/>
+      <c r="H199" s="2" t="inlineStr">
         <is>
           <t>Parcel Tax for Austrian B2C orders
  96
@@ -10493,39 +10600,39 @@
         </is>
       </c>
     </row>
-    <row r="198">
-      <c r="A198" s="2" t="inlineStr">
+    <row r="200">
+      <c r="A200" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B198" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C198" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D198" s="2" t="inlineStr">
+      <c r="B200" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C200" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D200" s="2" t="inlineStr">
         <is>
           <t>Sat, 12 Sep 2026 00:43:23 +0000</t>
         </is>
       </c>
-      <c r="E198" s="2" t="inlineStr">
+      <c r="E200" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F198" s="2" t="inlineStr">
+      <c r="F200" s="2" t="inlineStr">
         <is>
           <t>Votre paiement est en cours</t>
         </is>
       </c>
-      <c r="G198" s="2" t="inlineStr"/>
-      <c r="H198" s="2" t="inlineStr">
+      <c r="G200" s="2" t="inlineStr"/>
+      <c r="H200" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -10540,39 +10647,39 @@
         </is>
       </c>
     </row>
-    <row r="199">
-      <c r="A199" s="2" t="inlineStr">
+    <row r="201">
+      <c r="A201" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B199" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C199" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D199" s="2" t="inlineStr">
+      <c r="B201" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C201" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D201" s="2" t="inlineStr">
         <is>
           <t>Fri, 11 Sep 2026 14:08:42 +0000</t>
         </is>
       </c>
-      <c r="E199" s="2" t="inlineStr">
+      <c r="E201" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F199" s="2" t="inlineStr">
+      <c r="F201" s="2" t="inlineStr">
         <is>
           <t>通过 Q4 活动拓展您的业务 — 尽早提报，节省费用</t>
         </is>
       </c>
-      <c r="G199" s="2" t="inlineStr"/>
-      <c r="H199" s="2" t="inlineStr">
+      <c r="G201" s="2" t="inlineStr"/>
+      <c r="H201" s="2" t="inlineStr">
         <is>
           <t>最大化您的 Q4 业绩
 尊敬的卖家，
@@ -10604,39 +10711,39 @@
         </is>
       </c>
     </row>
-    <row r="200">
-      <c r="A200" s="2" t="inlineStr">
+    <row r="202">
+      <c r="A202" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B200" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C200" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D200" s="2" t="inlineStr">
+      <c r="B202" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C202" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D202" s="2" t="inlineStr">
         <is>
           <t>Thu, 10 Sep 2026 03:39:41 +0000</t>
         </is>
       </c>
-      <c r="E200" s="2" t="inlineStr">
+      <c r="E202" s="2" t="inlineStr">
         <is>
           <t>"Comunicados de Amazon Seller Central (no responder)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F200" s="2" t="inlineStr">
+      <c r="F202" s="2" t="inlineStr">
         <is>
           <t>[Amazon.es] Hemos suprimido uno o varios de tus listings de las búsquedas en la web de Amazon</t>
         </is>
       </c>
-      <c r="G200" s="2" t="inlineStr"/>
-      <c r="H200" s="2" t="inlineStr">
+      <c r="G202" s="2" t="inlineStr"/>
+      <c r="H202" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 [Amazon.es] Hemos suprimido uno o varios de tus listings de las búsquedas en la web de Amazon
@@ -10652,39 +10759,39 @@
         </is>
       </c>
     </row>
-    <row r="201">
-      <c r="A201" s="2" t="inlineStr">
+    <row r="203">
+      <c r="A203" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B201" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C201" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D201" s="2" t="inlineStr">
+      <c r="B203" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C203" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D203" s="2" t="inlineStr">
         <is>
           <t>Wed, 9 Sep 2026 16:45:36 +0000</t>
         </is>
       </c>
-      <c r="E201" s="2" t="inlineStr">
+      <c r="E203" s="2" t="inlineStr">
         <is>
           <t>Transparency No Reply &lt;noreply-transparency@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F201" s="2" t="inlineStr">
+      <c r="F203" s="2" t="inlineStr">
         <is>
           <t>OPR 体验优化——无需再手动追踪货件  /  Improvement to Your OPR Experience — No More Manual Shipment Tracking</t>
         </is>
       </c>
-      <c r="G201" s="2" t="inlineStr"/>
-      <c r="H201" s="2" t="inlineStr">
+      <c r="G203" s="2" t="inlineStr"/>
+      <c r="H203" s="2" t="inlineStr">
         <is>
           <t>尊敬的 Crifeton 团队：
 我们很高兴地通知您，OPR（Operational Performance Review运营表现评估）流程迎来一项优化，这将使开启 OPR 变得更加简单，并且您无需再手动追踪货件。
@@ -10708,39 +10815,39 @@
         </is>
       </c>
     </row>
-    <row r="202">
-      <c r="A202" s="2" t="inlineStr">
+    <row r="204">
+      <c r="A204" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B202" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C202" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D202" s="2" t="inlineStr">
+      <c r="B204" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C204" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D204" s="2" t="inlineStr">
         <is>
           <t>Wed, 9 Sep 2026 16:45:33 +0000</t>
         </is>
       </c>
-      <c r="E202" s="2" t="inlineStr">
+      <c r="E204" s="2" t="inlineStr">
         <is>
           <t>Transparency No Reply &lt;noreply-transparency@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F202" s="2" t="inlineStr">
+      <c r="F204" s="2" t="inlineStr">
         <is>
           <t>OPR 体验优化——无需再手动追踪货件  /  Improvement to Your OPR Experience — No More Manual Shipment Tracking</t>
         </is>
       </c>
-      <c r="G202" s="2" t="inlineStr"/>
-      <c r="H202" s="2" t="inlineStr">
+      <c r="G204" s="2" t="inlineStr"/>
+      <c r="H204" s="2" t="inlineStr">
         <is>
           <t>尊敬的 Crifeton 团队：
 我们很高兴地通知您，OPR（Operational Performance Review运营表现评估）流程迎来一项优化，这将使开启 OPR 变得更加简单，并且您无需再手动追踪货件。
@@ -10764,39 +10871,39 @@
         </is>
       </c>
     </row>
-    <row r="203">
-      <c r="A203" s="2" t="inlineStr">
+    <row r="205">
+      <c r="A205" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B203" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C203" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D203" s="2" t="inlineStr">
+      <c r="B205" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C205" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D205" s="2" t="inlineStr">
         <is>
           <t>Wed, 9 Sep 2026 14:40:23 +0000</t>
         </is>
       </c>
-      <c r="E203" s="2" t="inlineStr">
+      <c r="E205" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F203" s="2" t="inlineStr">
+      <c r="F205" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.ca Fulfillment by Amazon Merchant Invoice for 8/2026</t>
         </is>
       </c>
-      <c r="G203" s="2" t="inlineStr"/>
-      <c r="H203" s="2" t="inlineStr">
+      <c r="G205" s="2" t="inlineStr"/>
+      <c r="H205" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Your Amazon.ca Fulfillment by Amazon Merchant Invoice for 8/2026
  96
@@ -10818,39 +10925,39 @@
         </is>
       </c>
     </row>
-    <row r="204">
-      <c r="A204" s="2" t="inlineStr">
+    <row r="206">
+      <c r="A206" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B204" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C204" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D204" s="2" t="inlineStr">
+      <c r="B206" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C206" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D206" s="2" t="inlineStr">
         <is>
           <t>Tue, 8 Sep 2026 22:05:50 +0000</t>
         </is>
       </c>
-      <c r="E204" s="2" t="inlineStr">
+      <c r="E206" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F204" s="2" t="inlineStr">
+      <c r="F206" s="2" t="inlineStr">
         <is>
           <t>Envía la documentación de seguridad del producto para evitar la desactivación de los listados</t>
         </is>
       </c>
-      <c r="G204" s="2" t="inlineStr"/>
-      <c r="H204" s="2" t="inlineStr">
+      <c r="G206" s="2" t="inlineStr"/>
+      <c r="H206" s="2" t="inlineStr">
         <is>
           <t>96
  Hola, Weihai MX:
@@ -10867,39 +10974,39 @@
         </is>
       </c>
     </row>
-    <row r="205">
-      <c r="A205" s="2" t="inlineStr">
+    <row r="207">
+      <c r="A207" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B205" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C205" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D205" s="2" t="inlineStr">
+      <c r="B207" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C207" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D207" s="2" t="inlineStr">
         <is>
           <t>Tue, 8 Sep 2026 16:05:13 +0000</t>
         </is>
       </c>
-      <c r="E205" s="2" t="inlineStr">
+      <c r="E207" s="2" t="inlineStr">
         <is>
           <t>Amazon Services Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F205" s="2" t="inlineStr">
+      <c r="F207" s="2" t="inlineStr">
         <is>
           <t>Actualiza los precios de venta recomendados a más tardar el 9 de septiembre de 2026</t>
         </is>
       </c>
-      <c r="G205" s="2" t="inlineStr"/>
-      <c r="H205" s="2" t="inlineStr">
+      <c r="G207" s="2" t="inlineStr"/>
+      <c r="H207" s="2" t="inlineStr">
         <is>
           <t>96
  Las nuevas reglas para validar los precios de referencia entran en vigor el 9 de septiembre de 2026.
@@ -10913,39 +11020,39 @@
         </is>
       </c>
     </row>
-    <row r="206">
-      <c r="A206" s="2" t="inlineStr">
+    <row r="208">
+      <c r="A208" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B206" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C206" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D206" s="2" t="inlineStr">
+      <c r="B208" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C208" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D208" s="2" t="inlineStr">
         <is>
           <t>Sat, 26 Sep 2026 04:55:34 +0000</t>
         </is>
       </c>
-      <c r="E206" s="2" t="inlineStr">
+      <c r="E208" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F206" s="2" t="inlineStr">
+      <c r="F208" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G206" s="2" t="inlineStr"/>
-      <c r="H206" s="2" t="inlineStr">
+      <c r="G208" s="2" t="inlineStr"/>
+      <c r="H208" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -10968,39 +11075,39 @@
         </is>
       </c>
     </row>
-    <row r="207">
-      <c r="A207" s="2" t="inlineStr">
+    <row r="209">
+      <c r="A209" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B207" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C207" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D207" s="2" t="inlineStr">
+      <c r="B209" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C209" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D209" s="2" t="inlineStr">
         <is>
           <t>Sat, 26 Sep 2026 04:10:17 +0000</t>
         </is>
       </c>
-      <c r="E207" s="2" t="inlineStr">
+      <c r="E209" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F207" s="2" t="inlineStr">
+      <c r="F209" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-10-08</t>
         </is>
       </c>
-      <c r="G207" s="2" t="inlineStr"/>
-      <c r="H207" s="2" t="inlineStr">
+      <c r="G209" s="2" t="inlineStr"/>
+      <c r="H209" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -11024,39 +11131,39 @@
         </is>
       </c>
     </row>
-    <row r="208">
-      <c r="A208" s="2" t="inlineStr">
+    <row r="210">
+      <c r="A210" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B208" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C208" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D208" s="2" t="inlineStr">
+      <c r="B210" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C210" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D210" s="2" t="inlineStr">
         <is>
           <t>Wed, 23 Sep 2026 17:17:49 +0000</t>
         </is>
       </c>
-      <c r="E208" s="2" t="inlineStr">
+      <c r="E210" s="2" t="inlineStr">
         <is>
           <t>The Fulfillment by Amazon team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F208" s="2" t="inlineStr">
+      <c r="F210" s="2" t="inlineStr">
         <is>
           <t>Remove aged, stranded, and unfulfillable inventory by 22nd Oct 2026</t>
         </is>
       </c>
-      <c r="G208" s="2" t="inlineStr"/>
-      <c r="H208" s="2" t="inlineStr">
+      <c r="G210" s="2" t="inlineStr"/>
+      <c r="H210" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 This title will display on mobile devices
@@ -11071,39 +11178,39 @@
         </is>
       </c>
     </row>
-    <row r="209">
-      <c r="A209" s="2" t="inlineStr">
+    <row r="211">
+      <c r="A211" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B209" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C209" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D209" s="2" t="inlineStr">
+      <c r="B211" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C211" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D211" s="2" t="inlineStr">
         <is>
           <t>Sat, 19 Sep 2026 04:29:10 +0000</t>
         </is>
       </c>
-      <c r="E209" s="2" t="inlineStr">
+      <c r="E211" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F209" s="2" t="inlineStr">
+      <c r="F211" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-10-01</t>
         </is>
       </c>
-      <c r="G209" s="2" t="inlineStr"/>
-      <c r="H209" s="2" t="inlineStr">
+      <c r="G211" s="2" t="inlineStr"/>
+      <c r="H211" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -11124,39 +11231,39 @@
         </is>
       </c>
     </row>
-    <row r="210">
-      <c r="A210" s="2" t="inlineStr">
+    <row r="212">
+      <c r="A212" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B210" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C210" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D210" s="2" t="inlineStr">
+      <c r="B212" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C212" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D212" s="2" t="inlineStr">
         <is>
           <t>Sat, 19 Sep 2026 03:52:36 +0000</t>
         </is>
       </c>
-      <c r="E210" s="2" t="inlineStr">
+      <c r="E212" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F210" s="2" t="inlineStr">
+      <c r="F212" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G210" s="2" t="inlineStr"/>
-      <c r="H210" s="2" t="inlineStr">
+      <c r="G212" s="2" t="inlineStr"/>
+      <c r="H212" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -11180,39 +11287,39 @@
         </is>
       </c>
     </row>
-    <row r="211">
-      <c r="A211" s="2" t="inlineStr">
+    <row r="213">
+      <c r="A213" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B211" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C211" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D211" s="2" t="inlineStr">
+      <c r="B213" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C213" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D213" s="2" t="inlineStr">
         <is>
           <t>Thu, 17 Sep 2026 13:54:38 +0000</t>
         </is>
       </c>
-      <c r="E211" s="2" t="inlineStr">
+      <c r="E213" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F211" s="2" t="inlineStr">
+      <c r="F213" s="2" t="inlineStr">
         <is>
           <t>Stranded SKUs scheduled for automatic removal</t>
         </is>
       </c>
-      <c r="G211" s="2" t="inlineStr"/>
-      <c r="H211" s="2" t="inlineStr">
+      <c r="G213" s="2" t="inlineStr"/>
+      <c r="H213" s="2" t="inlineStr">
         <is>
           <t>96
 Stranded SKUs scheduled for automatic removal
@@ -11224,40 +11331,40 @@
         </is>
       </c>
     </row>
-    <row r="212">
-      <c r="A212" s="2" t="inlineStr">
+    <row r="214">
+      <c r="A214" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B212" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C212" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D212" s="2" t="inlineStr">
+      <c r="B214" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C214" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D214" s="2" t="inlineStr">
         <is>
           <t>Thu, 17 Sep 2026 09:46:06 +0000</t>
         </is>
       </c>
-      <c r="E212" s="2" t="inlineStr">
+      <c r="E214" s="2" t="inlineStr">
         <is>
           <t>"seller-coaching-m@amazon.com" &lt;seller-coaching-m@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F212" s="2" t="inlineStr">
+      <c r="F214" s="2" t="inlineStr">
         <is>
           <t>[Case ID:13247704742]"Your Case Resolved" Optimize Your Next EU FBA
  Shipment Based on Inventory Health [A-AWD]</t>
         </is>
       </c>
-      <c r="G212" s="2" t="inlineStr"/>
-      <c r="H212" s="2" t="inlineStr">
+      <c r="G214" s="2" t="inlineStr"/>
+      <c r="H214" s="2" t="inlineStr">
         <is>
           <t>96
 [Case ID:13247704742]"Your Case Resolved" Optimize Your Next EU FBA Shipment Based on Inventory Health [A-AWD]
@@ -11276,39 +11383,39 @@
         </is>
       </c>
     </row>
-    <row r="213">
-      <c r="A213" s="2" t="inlineStr">
+    <row r="215">
+      <c r="A215" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B213" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C213" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D213" s="2" t="inlineStr">
+      <c r="B215" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C215" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D215" s="2" t="inlineStr">
         <is>
           <t>Sat, 12 Sep 2026 04:18:39 +0000</t>
         </is>
       </c>
-      <c r="E213" s="2" t="inlineStr">
+      <c r="E215" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F213" s="2" t="inlineStr">
+      <c r="F215" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-09-24</t>
         </is>
       </c>
-      <c r="G213" s="2" t="inlineStr"/>
-      <c r="H213" s="2" t="inlineStr">
+      <c r="G215" s="2" t="inlineStr"/>
+      <c r="H215" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -11331,40 +11438,40 @@
         </is>
       </c>
     </row>
-    <row r="214">
-      <c r="A214" s="2" t="inlineStr">
+    <row r="216">
+      <c r="A216" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B214" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C214" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D214" s="2" t="inlineStr">
+      <c r="B216" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C216" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D216" s="2" t="inlineStr">
         <is>
           <t>Fri, 11 Sep 2026 09:43:34 +0000</t>
         </is>
       </c>
-      <c r="E214" s="2" t="inlineStr">
+      <c r="E216" s="2" t="inlineStr">
         <is>
           <t>"seller-coaching-m@amazon.com" &lt;seller-coaching-m@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F214" s="2" t="inlineStr">
+      <c r="F216" s="2" t="inlineStr">
         <is>
           <t>[Case ID:13247704742]"Your Help Needed" Optimize Your Next EU FBA
  Shipment Based on Inventory Health [A-AWD]</t>
         </is>
       </c>
-      <c r="G214" s="2" t="inlineStr"/>
-      <c r="H214" s="2" t="inlineStr">
+      <c r="G216" s="2" t="inlineStr"/>
+      <c r="H216" s="2" t="inlineStr">
         <is>
           <t>96
 [Case ID:13247704742]"Your Help Needed" Optimize Your Next EU FBA Shipment Based on Inventory Health [A-AWD]
@@ -11382,39 +11489,39 @@
         </is>
       </c>
     </row>
-    <row r="215">
-      <c r="A215" s="2" t="inlineStr">
+    <row r="217">
+      <c r="A217" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B215" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C215" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D215" s="2" t="inlineStr">
+      <c r="B217" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C217" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D217" s="2" t="inlineStr">
         <is>
           <t>Thu, 1 Oct 2026 21:27:08 +0000</t>
         </is>
       </c>
-      <c r="E215" s="2" t="inlineStr">
+      <c r="E217" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F215" s="2" t="inlineStr">
+      <c r="F217" s="2" t="inlineStr">
         <is>
           <t>A passkey is required for account access starting in two weeks</t>
         </is>
       </c>
-      <c r="G215" s="2" t="inlineStr"/>
-      <c r="H215" s="2" t="inlineStr">
+      <c r="G217" s="2" t="inlineStr"/>
+      <c r="H217" s="2" t="inlineStr">
         <is>
           <t>96
  For security, set up passkey login to maintain account access
@@ -11430,39 +11537,39 @@
         </is>
       </c>
     </row>
-    <row r="216">
-      <c r="A216" s="2" t="inlineStr">
+    <row r="218">
+      <c r="A218" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B216" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C216" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D216" s="2" t="inlineStr">
+      <c r="B218" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C218" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D218" s="2" t="inlineStr">
         <is>
           <t>Thu, 1 Oct 2026 04:58:43 +0000</t>
         </is>
       </c>
-      <c r="E216" s="2" t="inlineStr">
+      <c r="E218" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F216" s="2" t="inlineStr">
+      <c r="F218" s="2" t="inlineStr">
         <is>
           <t>A returns experience customers actually like</t>
         </is>
       </c>
-      <c r="G216" s="2" t="inlineStr"/>
-      <c r="H216" s="2" t="inlineStr">
+      <c r="G218" s="2" t="inlineStr"/>
+      <c r="H218" s="2" t="inlineStr">
         <is>
           <t>96
  Faster resolutions for buyers, less friction for you.
@@ -11487,39 +11594,39 @@
         </is>
       </c>
     </row>
-    <row r="217">
-      <c r="A217" s="2" t="inlineStr">
+    <row r="219">
+      <c r="A219" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B217" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C217" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D217" s="2" t="inlineStr">
+      <c r="B219" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C219" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D219" s="2" t="inlineStr">
         <is>
           <t>Thu, 1 Oct 2026 00:17:41 +0000</t>
         </is>
       </c>
-      <c r="E217" s="2" t="inlineStr">
+      <c r="E219" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F217" s="2" t="inlineStr">
+      <c r="F219" s="2" t="inlineStr">
         <is>
           <t>View your US Q4-2026 CSBA fee rate</t>
         </is>
       </c>
-      <c r="G217" s="2" t="inlineStr"/>
-      <c r="H217" s="2" t="inlineStr">
+      <c r="G219" s="2" t="inlineStr"/>
+      <c r="H219" s="2" t="inlineStr">
         <is>
           <t>96
  (Important) CSBA US Fee rate for Q4-2026
@@ -11549,39 +11656,39 @@
         </is>
       </c>
     </row>
-    <row r="218">
-      <c r="A218" s="2" t="inlineStr">
+    <row r="220">
+      <c r="A220" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B218" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C218" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D218" s="2" t="inlineStr">
+      <c r="B220" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C220" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D220" s="2" t="inlineStr">
         <is>
           <t>Wed, 23 Sep 2026 10:37:18 +0800 (CST)</t>
         </is>
       </c>
-      <c r="E218" s="2" t="inlineStr">
+      <c r="E220" s="2" t="inlineStr">
         <is>
           <t>能标检测(NBTS）亚马逊DV-TRF号管理 &lt;fli.lin@nbtscn.com&gt;</t>
         </is>
       </c>
-      <c r="F218" s="2" t="inlineStr">
+      <c r="F220" s="2" t="inlineStr">
         <is>
           <t>能标检测(NBTS）亚马逊DV-TRF号情况跟进</t>
         </is>
       </c>
-      <c r="G218" s="2" t="inlineStr"/>
-      <c r="H218" s="2" t="inlineStr">
+      <c r="G220" s="2" t="inlineStr"/>
+      <c r="H220" s="2" t="inlineStr">
         <is>
           <t>尊敬的客户：
 您好！
@@ -11610,39 +11717,39 @@
         </is>
       </c>
     </row>
-    <row r="219">
-      <c r="A219" s="2" t="inlineStr">
+    <row r="221">
+      <c r="A221" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B219" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C219" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D219" s="2" t="inlineStr">
+      <c r="B221" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C221" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D221" s="2" t="inlineStr">
         <is>
           <t>Wed, 23 Sep 2026 01:44:18 +0000</t>
         </is>
       </c>
-      <c r="E219" s="2" t="inlineStr">
+      <c r="E221" s="2" t="inlineStr">
         <is>
           <t>"Amazon Seller Central Notifications (Do Not Reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F219" s="2" t="inlineStr">
+      <c r="F221" s="2" t="inlineStr">
         <is>
           <t>Dangerous goods (hazmat) status update</t>
         </is>
       </c>
-      <c r="G219" s="2" t="inlineStr"/>
-      <c r="H219" s="2" t="inlineStr">
+      <c r="G221" s="2" t="inlineStr"/>
+      <c r="H221" s="2" t="inlineStr">
         <is>
           <t>96
  Dangerous goods (hazmat) status update
@@ -11664,39 +11771,39 @@
         </is>
       </c>
     </row>
-    <row r="220">
-      <c r="A220" s="2" t="inlineStr">
+    <row r="222">
+      <c r="A222" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B220" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C220" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D220" s="2" t="inlineStr">
+      <c r="B222" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C222" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D222" s="2" t="inlineStr">
         <is>
           <t>Tue, 22 Sep 2026 10:57:46 +0800 (CST)</t>
         </is>
       </c>
-      <c r="E220" s="2" t="inlineStr">
+      <c r="E222" s="2" t="inlineStr">
         <is>
           <t>能标检测(NBTS）亚马逊DV-TRF号管理 &lt;fli.lin@nbtscn.com&gt;</t>
         </is>
       </c>
-      <c r="F220" s="2" t="inlineStr">
+      <c r="F222" s="2" t="inlineStr">
         <is>
           <t>能标检测(NBTS）亚马逊DV-TRF号情况跟进</t>
         </is>
       </c>
-      <c r="G220" s="2" t="inlineStr"/>
-      <c r="H220" s="2" t="inlineStr">
+      <c r="G222" s="2" t="inlineStr"/>
+      <c r="H222" s="2" t="inlineStr">
         <is>
           <t>尊敬的客户：
 您好！
@@ -11724,40 +11831,40 @@
         </is>
       </c>
     </row>
-    <row r="221">
-      <c r="A221" s="2" t="inlineStr">
+    <row r="223">
+      <c r="A223" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B221" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C221" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D221" s="2" t="inlineStr">
+      <c r="B223" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C223" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D223" s="2" t="inlineStr">
         <is>
           <t>Mon, 21 Sep 2026 21:52:15 +0000</t>
         </is>
       </c>
-      <c r="E221" s="2" t="inlineStr">
+      <c r="E223" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F221" s="2" t="inlineStr">
+      <c r="F223" s="2" t="inlineStr">
         <is>
           <t>FBA Grade and Resell is now Sell as Used and includes refurbished
  items</t>
         </is>
       </c>
-      <c r="G221" s="2" t="inlineStr"/>
-      <c r="H221" s="2" t="inlineStr">
+      <c r="G223" s="2" t="inlineStr"/>
+      <c r="H223" s="2" t="inlineStr">
         <is>
           <t>96
  Recover more value from your eligible FBA returns.
@@ -11772,39 +11879,39 @@
         </is>
       </c>
     </row>
-    <row r="222">
-      <c r="A222" s="2" t="inlineStr">
+    <row r="224">
+      <c r="A224" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B222" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C222" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D222" s="2" t="inlineStr">
+      <c r="B224" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C224" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D224" s="2" t="inlineStr">
         <is>
           <t>Mon, 21 Sep 2026 10:15:39 +0800 (CST)</t>
         </is>
       </c>
-      <c r="E222" s="2" t="inlineStr">
+      <c r="E224" s="2" t="inlineStr">
         <is>
           <t>能标检测(NBTS）亚马逊DV-TRF号管理 &lt;fli.lin@nbtscn.com&gt;</t>
         </is>
       </c>
-      <c r="F222" s="2" t="inlineStr">
+      <c r="F224" s="2" t="inlineStr">
         <is>
           <t>能标检测(NBTS）亚马逊DV-TRF号情况跟进</t>
         </is>
       </c>
-      <c r="G222" s="2" t="inlineStr"/>
-      <c r="H222" s="2" t="inlineStr">
+      <c r="G224" s="2" t="inlineStr"/>
+      <c r="H224" s="2" t="inlineStr">
         <is>
           <t>尊敬的客户：
 您好！
@@ -11832,39 +11939,39 @@
         </is>
       </c>
     </row>
-    <row r="223">
-      <c r="A223" s="2" t="inlineStr">
+    <row r="225">
+      <c r="A225" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B223" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C223" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D223" s="2" t="inlineStr">
+      <c r="B225" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C225" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D225" s="2" t="inlineStr">
         <is>
           <t>Thu, 17 Sep 2026 13:51:44 +0000</t>
         </is>
       </c>
-      <c r="E223" s="2" t="inlineStr">
+      <c r="E225" s="2" t="inlineStr">
         <is>
           <t>Amazon Multichannel Fulfilment Team &lt;multichannelfulfillment@supplychain.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F223" s="2" t="inlineStr">
+      <c r="F225" s="2" t="inlineStr">
         <is>
           <t>Your peak prep checklist is ready</t>
         </is>
       </c>
-      <c r="G223" s="2" t="inlineStr"/>
-      <c r="H223" s="2" t="inlineStr">
+      <c r="G225" s="2" t="inlineStr"/>
+      <c r="H225" s="2" t="inlineStr">
         <is>
           <t>Your peak prep checklist is ready
 Position inventory, activate savings, and make your delivery speed visible. ‌ ‌ ‌ ‌ ‌ ‌ ‌ ‌ ‌ ‌ ‌ ‌ ‌ ‌ ‌ ‌ ‌ ‌
@@ -11880,39 +11987,39 @@
         </is>
       </c>
     </row>
-    <row r="224">
-      <c r="A224" s="2" t="inlineStr">
+    <row r="226">
+      <c r="A226" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B224" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C224" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D224" s="2" t="inlineStr">
+      <c r="B226" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C226" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D226" s="2" t="inlineStr">
         <is>
           <t>Wed, 16 Sep 2026 01:31:48 +0000</t>
         </is>
       </c>
-      <c r="E224" s="2" t="inlineStr">
+      <c r="E226" s="2" t="inlineStr">
         <is>
           <t>"Amazon Seller Central Notifications (Do Not Reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F224" s="2" t="inlineStr">
+      <c r="F226" s="2" t="inlineStr">
         <is>
           <t>Dangerous goods (hazmat) status update</t>
         </is>
       </c>
-      <c r="G224" s="2" t="inlineStr"/>
-      <c r="H224" s="2" t="inlineStr">
+      <c r="G226" s="2" t="inlineStr"/>
+      <c r="H226" s="2" t="inlineStr">
         <is>
           <t>96
  Dangerous goods (hazmat) status update
@@ -11935,39 +12042,39 @@
         </is>
       </c>
     </row>
-    <row r="225">
-      <c r="A225" s="2" t="inlineStr">
+    <row r="227">
+      <c r="A227" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B225" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C225" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D225" s="2" t="inlineStr">
+      <c r="B227" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C227" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D227" s="2" t="inlineStr">
         <is>
           <t>Tue, 15 Sep 2026 10:27:49 +0800 (CST)</t>
         </is>
       </c>
-      <c r="E225" s="2" t="inlineStr">
+      <c r="E227" s="2" t="inlineStr">
         <is>
           <t>能标检测(NBTS）亚马逊DV-TRF号管理 &lt;fli.lin@nbtscn.com&gt;</t>
         </is>
       </c>
-      <c r="F225" s="2" t="inlineStr">
+      <c r="F227" s="2" t="inlineStr">
         <is>
           <t>能标检测(NBTS）亚马逊DV-TRF号情况跟进</t>
         </is>
       </c>
-      <c r="G225" s="2" t="inlineStr"/>
-      <c r="H225" s="2" t="inlineStr">
+      <c r="G227" s="2" t="inlineStr"/>
+      <c r="H227" s="2" t="inlineStr">
         <is>
           <t>尊敬的客户：
 您好！
@@ -11995,39 +12102,39 @@
         </is>
       </c>
     </row>
-    <row r="226">
-      <c r="A226" s="2" t="inlineStr">
+    <row r="228">
+      <c r="A228" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B226" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C226" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D226" s="2" t="inlineStr">
+      <c r="B228" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C228" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D228" s="2" t="inlineStr">
         <is>
           <t>Mon, 14 Sep 2026 14:01:06 +0000</t>
         </is>
       </c>
-      <c r="E226" s="2" t="inlineStr">
+      <c r="E228" s="2" t="inlineStr">
         <is>
           <t>The Amazon Services team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F226" s="2" t="inlineStr">
+      <c r="F228" s="2" t="inlineStr">
         <is>
           <t>Redesigned Seller Central becomes default 24 Sep</t>
         </is>
       </c>
-      <c r="G226" s="2" t="inlineStr"/>
-      <c r="H226" s="2" t="inlineStr">
+      <c r="G228" s="2" t="inlineStr"/>
+      <c r="H228" s="2" t="inlineStr">
         <is>
           <t>96
  Same powerful tools, built to grow with your business.
@@ -12042,40 +12149,40 @@
         </is>
       </c>
     </row>
-    <row r="227">
-      <c r="A227" s="2" t="inlineStr">
+    <row r="229">
+      <c r="A229" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B227" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C227" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D227" s="2" t="inlineStr">
+      <c r="B229" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C229" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D229" s="2" t="inlineStr">
         <is>
           <t>Thu, 10 Sep 2026 03:24:54 +0000</t>
         </is>
       </c>
-      <c r="E227" s="2" t="inlineStr">
+      <c r="E229" s="2" t="inlineStr">
         <is>
           <t>"Amazon Seller Central Communications (Do Not Reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F227" s="2" t="inlineStr">
+      <c r="F229" s="2" t="inlineStr">
         <is>
           <t>[Amazon.fr] One or More of Your Amazon Listings Have Been Search
  Suppressed</t>
         </is>
       </c>
-      <c r="G227" s="2" t="inlineStr"/>
-      <c r="H227" s="2" t="inlineStr">
+      <c r="G229" s="2" t="inlineStr"/>
+      <c r="H229" s="2" t="inlineStr">
         <is>
           <t>96
 [Amazon.fr] One or More of Your Amazon Listings Have Been Search Suppressed
